--- a/OurLib.xlsx
+++ b/OurLib.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\00_OnWork\01_GITLAB_REPOS\my-altium-library\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\my-altium-library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4760343-4C86-4F6C-9DDE-58248BB6E9A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3D4BE84-BE95-43AF-88A1-F13085CF9430}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="14790" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01 - Резисторы" sheetId="1" r:id="rId1"/>
@@ -31,6 +31,9 @@
   </sheets>
   <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="179">
   <si>
     <t>Part Number</t>
   </si>
@@ -567,6 +570,15 @@
   </si>
   <si>
     <t>LEDs.PcbLib</t>
+  </si>
+  <si>
+    <t>Bat</t>
+  </si>
+  <si>
+    <t>Батарейка гальваническая</t>
+  </si>
+  <si>
+    <t>Батарейка</t>
   </si>
 </sst>
 </file>
@@ -2075,7 +2087,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.28515625" customWidth="1"/>
@@ -2198,6 +2210,20 @@
       </c>
       <c r="K4" t="s">
         <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>176</v>
+      </c>
+      <c r="B5" t="s">
+        <v>178</v>
+      </c>
+      <c r="C5" t="s">
+        <v>177</v>
+      </c>
+      <c r="D5" t="s">
+        <v>176</v>
       </c>
     </row>
   </sheetData>

--- a/OurLib.xlsx
+++ b/OurLib.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\my-altium-library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3D4BE84-BE95-43AF-88A1-F13085CF9430}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FF46E9D-EA3E-4BD5-B8A6-EA4FFAFB8AB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="14790" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="10965" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01 - Резисторы" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="181">
   <si>
     <t>Part Number</t>
   </si>
@@ -579,6 +579,12 @@
   </si>
   <si>
     <t>Батарейка</t>
+  </si>
+  <si>
+    <t>Resistor_M</t>
+  </si>
+  <si>
+    <t>Переменный резистор</t>
   </si>
 </sst>
 </file>
@@ -816,7 +822,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -901,6 +907,17 @@
       </c>
       <c r="K2" t="s">
         <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D3" t="s">
+        <v>179</v>
+      </c>
+      <c r="J3" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/OurLib.xlsx
+++ b/OurLib.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="14"/>
   </bookViews>
   <sheets>
     <sheet name="01 - Резисторы" sheetId="1" state="visible" r:id="rId3"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="203">
   <si>
     <t xml:space="preserve">Part Number</t>
   </si>
@@ -183,6 +183,12 @@
     <t xml:space="preserve">DFN-8</t>
   </si>
   <si>
+    <t xml:space="preserve">DFN.PcbLib</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buzzer</t>
+  </si>
+  <si>
     <t xml:space="preserve">BQ24072RGTR</t>
   </si>
   <si>
@@ -321,6 +327,9 @@
     <t xml:space="preserve">Усилитель</t>
   </si>
   <si>
+    <t xml:space="preserve">SOIC-8</t>
+  </si>
+  <si>
     <t xml:space="preserve">PCF8574T</t>
   </si>
   <si>
@@ -624,7 +633,16 @@
     <t xml:space="preserve">ИК- диод</t>
   </si>
   <si>
+    <t xml:space="preserve">Hinged_Diod</t>
+  </si>
+  <si>
     <t xml:space="preserve">SFH 4550</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Светодиод RGB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LED_RGB</t>
   </si>
 </sst>
 </file>
@@ -1072,82 +1090,82 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>119</v>
-      </c>
       <c r="J3" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>120</v>
-      </c>
       <c r="K4" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -1230,338 +1248,338 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>128</v>
-      </c>
       <c r="D3" s="1" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>133</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>135</v>
-      </c>
       <c r="D6" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -1642,39 +1660,39 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="J3" s="1" t="s">
-        <v>173</v>
-      </c>
       <c r="K3" s="1" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -1755,22 +1773,22 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
   </sheetData>
@@ -1847,22 +1865,22 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -1881,7 +1899,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr defaultColWidth="8.71484375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.14"/>
@@ -1943,50 +1961,82 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>110</v>
+      <c r="K3" s="1" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="B4" s="1" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="K5" s="1" t="s">
         <v>196</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -2137,7 +2187,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr defaultColWidth="8.71484375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22.43"/>
@@ -2278,6 +2328,32 @@
       </c>
       <c r="J5" s="1" t="s">
         <v>39</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -2354,22 +2430,22 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>49</v>
-      </c>
       <c r="E2" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>40</v>
@@ -2377,114 +2453,117 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="K3" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="K5" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="J7" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="K7" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -2565,39 +2644,39 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>70</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>40</v>
@@ -2605,42 +2684,42 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -2722,88 +2801,94 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="E2" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>85</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="K5" s="1" t="s">
         <v>94</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -2880,25 +2965,25 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -2978,19 +3063,19 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>21</v>
@@ -3072,80 +3157,80 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>110</v>
-      </c>
       <c r="K3" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/OurLib.xlsx
+++ b/OurLib.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\my-altium-library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FF46E9D-EA3E-4BD5-B8A6-EA4FFAFB8AB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B905836B-4780-4C54-BE10-9FC574F32AB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="10965" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="13485" tabRatio="785" firstSheet="5" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01 - Резисторы" sheetId="1" r:id="rId1"/>
@@ -28,6 +28,7 @@
     <sheet name="14 - Кнопки" sheetId="13" r:id="rId13"/>
     <sheet name="15 - Моторы" sheetId="14" r:id="rId14"/>
     <sheet name="16 - Светодиоды" sheetId="15" r:id="rId15"/>
+    <sheet name="17 - Акустика" sheetId="17" r:id="rId16"/>
   </sheets>
   <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="184">
   <si>
     <t>Part Number</t>
   </si>
@@ -585,6 +586,15 @@
   </si>
   <si>
     <t>Переменный резистор</t>
+  </si>
+  <si>
+    <t>Динамик</t>
+  </si>
+  <si>
+    <t>BA</t>
+  </si>
+  <si>
+    <t>BA.SchLib</t>
   </si>
 </sst>
 </file>
@@ -1844,6 +1854,88 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A5B92C0-7314-4F98-B126-6DD0035054E9}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.140625" customWidth="1"/>
+    <col min="2" max="2" width="15.42578125" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" customWidth="1"/>
+    <col min="4" max="4" width="11.140625" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" customWidth="1"/>
+    <col min="7" max="7" width="13.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.28515625" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" customWidth="1"/>
+    <col min="11" max="11" width="28.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2" t="s">
+        <v>182</v>
+      </c>
+      <c r="J2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:N3"/>

--- a/OurLib.xlsx
+++ b/OurLib.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12285" tabRatio="500" firstSheet="2" activeTab="8"/>
+    <workbookView windowWidth="28800" windowHeight="12885" tabRatio="500" firstSheet="8" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="01 - Резисторы" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="208">
   <si>
     <t>Part Number</t>
   </si>
@@ -437,6 +437,15 @@
   </si>
   <si>
     <t>PMOSFET</t>
+  </si>
+  <si>
+    <t>двойной N Мосфет</t>
+  </si>
+  <si>
+    <t>NMOSFETx2</t>
+  </si>
+  <si>
+    <t>TSOP-6</t>
   </si>
   <si>
     <t>PROG UART</t>
@@ -1828,8 +1837,8 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N5"/>
-  <sheetFormatPr defaultColWidth="8.71428571428571" defaultRowHeight="15" outlineLevelRow="4"/>
+  <dimension ref="A1:N6"/>
+  <sheetFormatPr defaultColWidth="8.71428571428571" defaultRowHeight="15" outlineLevelRow="5"/>
   <cols>
     <col min="1" max="1" width="28.8571428571429" style="1" customWidth="1"/>
     <col min="2" max="2" width="15.2857142857143" style="1" customWidth="1"/>
@@ -1965,6 +1974,26 @@
       </c>
       <c r="K5" s="1" t="s">
         <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -2041,338 +2070,338 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>133</v>
-      </c>
       <c r="D3" s="1" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>138</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="1" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>140</v>
-      </c>
       <c r="D6" s="1" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="1" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="1" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="1" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="1" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="1" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" s="1" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="1" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="1" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="1" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -2447,39 +2476,39 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="J3" s="1" t="s">
-        <v>178</v>
-      </c>
       <c r="K3" s="1" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
   </sheetData>
@@ -2554,22 +2583,22 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>
@@ -2640,22 +2669,22 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
   </sheetData>
@@ -2730,82 +2759,82 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="E3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>201</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="1" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="E4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>201</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="1" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>

--- a/OurLib.xlsx
+++ b/OurLib.xlsx
@@ -4,24 +4,25 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12885" tabRatio="500" firstSheet="8" activeTab="9"/>
+    <workbookView windowWidth="28800" windowHeight="12885" tabRatio="500" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="01 - Резисторы" sheetId="1" r:id="rId1"/>
     <sheet name="02 - Конденсаторы" sheetId="2" r:id="rId2"/>
-    <sheet name="04 - Датчики" sheetId="3" r:id="rId3"/>
-    <sheet name="05 - Питание" sheetId="4" r:id="rId4"/>
-    <sheet name="06 - Микроконтроллеры" sheetId="5" r:id="rId5"/>
-    <sheet name="07 - Логика" sheetId="6" r:id="rId6"/>
-    <sheet name="08 - Интерфейсы" sheetId="7" r:id="rId7"/>
-    <sheet name="09 - Кварцы" sheetId="8" r:id="rId8"/>
-    <sheet name="10 - Диоды" sheetId="9" r:id="rId9"/>
-    <sheet name="11 - Транзисторы" sheetId="10" r:id="rId10"/>
-    <sheet name="12 - Разъемы" sheetId="11" r:id="rId11"/>
-    <sheet name="13 - Антенны" sheetId="12" r:id="rId12"/>
-    <sheet name="14 - Кнопки" sheetId="13" r:id="rId13"/>
-    <sheet name="15 - Моторы" sheetId="14" r:id="rId14"/>
-    <sheet name="16 - Светодиоды" sheetId="15" r:id="rId15"/>
+    <sheet name="03 - Индуктивность" sheetId="16" r:id="rId3"/>
+    <sheet name="04 - Датчики" sheetId="3" r:id="rId4"/>
+    <sheet name="05 - Питание" sheetId="4" r:id="rId5"/>
+    <sheet name="06 - Микроконтроллеры" sheetId="5" r:id="rId6"/>
+    <sheet name="07 - Логика" sheetId="6" r:id="rId7"/>
+    <sheet name="08 - Интерфейсы" sheetId="7" r:id="rId8"/>
+    <sheet name="09 - Кварцы" sheetId="8" r:id="rId9"/>
+    <sheet name="10 - Диоды" sheetId="9" r:id="rId10"/>
+    <sheet name="11 - Транзисторы" sheetId="10" r:id="rId11"/>
+    <sheet name="12 - Разъемы" sheetId="11" r:id="rId12"/>
+    <sheet name="13 - Антенны" sheetId="12" r:id="rId13"/>
+    <sheet name="14 - Кнопки" sheetId="13" r:id="rId14"/>
+    <sheet name="15 - Моторы" sheetId="14" r:id="rId15"/>
+    <sheet name="16 - Светодиоды" sheetId="15" r:id="rId16"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="216">
   <si>
     <t>Part Number</t>
   </si>
@@ -148,6 +149,18 @@
     <t>CSMD_7343_P</t>
   </si>
   <si>
+    <t>Inductance coil</t>
+  </si>
+  <si>
+    <t>Катушка индуктивности</t>
+  </si>
+  <si>
+    <t>Со стержнем</t>
+  </si>
+  <si>
+    <t>Inductance.SchLib</t>
+  </si>
+  <si>
     <t>AD8232</t>
   </si>
   <si>
@@ -194,6 +207,18 @@
   </si>
   <si>
     <t>Buzzer</t>
+  </si>
+  <si>
+    <t>MQ-131</t>
+  </si>
+  <si>
+    <t>Датчик воздуха</t>
+  </si>
+  <si>
+    <t>MQ (6)</t>
+  </si>
+  <si>
+    <t>Sensors.PcbLib</t>
   </si>
   <si>
     <t>BQ24072RGTR</t>
@@ -1837,6 +1862,173 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A1:N5"/>
+  <sheetFormatPr defaultColWidth="8.71428571428571" defaultRowHeight="15" outlineLevelRow="4"/>
+  <cols>
+    <col min="1" max="1" width="17" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5714285714286" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.2857142857143" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.8571428571429" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.8571428571429" style="1" customWidth="1"/>
+    <col min="6" max="9" width="13.2857142857143" style="1" customWidth="1"/>
+    <col min="10" max="10" width="18" style="1" customWidth="1"/>
+    <col min="11" max="11" width="30" style="1" customWidth="1"/>
+    <col min="12" max="12" width="5.57142857142857" style="1" customWidth="1"/>
+    <col min="13" max="14" width="5.28571428571429" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:N6"/>
   <sheetFormatPr defaultColWidth="8.71428571428571" defaultRowHeight="15" outlineLevelRow="5"/>
   <cols>
@@ -1898,102 +2090,102 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="1" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>121</v>
-      </c>
       <c r="J4" s="1" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="1" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="1" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="J6" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>125</v>
-      </c>
       <c r="K6" s="1" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -2003,7 +2195,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:N16"/>
@@ -2070,338 +2262,338 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="1" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="1" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="F5" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="J5" s="1" t="s">
-        <v>137</v>
-      </c>
       <c r="K5" s="1" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="K6" s="1" t="s">
         <v>146</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="1" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="1" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="1" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="1" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="1" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" s="1" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="1" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="1" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="1" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="1" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
     </row>
   </sheetData>
@@ -2411,7 +2603,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:N3"/>
@@ -2476,39 +2668,39 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -2518,7 +2710,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:N2"/>
@@ -2583,22 +2775,22 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>
@@ -2608,7 +2800,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:N2"/>
@@ -2669,22 +2861,22 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>
@@ -2694,7 +2886,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:N5"/>
@@ -2759,82 +2951,82 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="1" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="1" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
   </sheetData>
@@ -2973,8 +3165,89 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N6"/>
-  <sheetFormatPr defaultColWidth="8.71428571428571" defaultRowHeight="15" outlineLevelRow="5"/>
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="1"/>
+  <cols>
+    <col min="1" max="1" width="16.5714285714286" customWidth="1"/>
+    <col min="2" max="2" width="24.4285714285714" customWidth="1"/>
+    <col min="3" max="3" width="18.8571428571429" customWidth="1"/>
+    <col min="4" max="4" width="17.7142857142857" customWidth="1"/>
+    <col min="10" max="10" width="19.8571428571429" customWidth="1"/>
+    <col min="11" max="11" width="17" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:N7"/>
+  <sheetFormatPr defaultColWidth="8.71428571428571" defaultRowHeight="15" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="1" width="22.4285714285714" style="1" customWidth="1"/>
     <col min="2" max="2" width="16.7142857142857" style="1" customWidth="1"/>
@@ -3035,111 +3308,134 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -3149,7 +3445,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:N7"/>
@@ -3210,140 +3506,140 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="1" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="K5" s="1" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="1" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="K6" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="1" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -3353,7 +3649,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:N5"/>
@@ -3418,82 +3714,82 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="1" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>70</v>
-      </c>
       <c r="D5" s="1" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -3503,7 +3799,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:N5"/>
@@ -3569,94 +3865,94 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="1" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>84</v>
-      </c>
       <c r="K4" s="1" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="1" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -3666,7 +3962,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:N2"/>
@@ -3727,25 +4023,25 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="J2" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>102</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -3755,7 +4051,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:N2"/>
@@ -3819,189 +4115,22 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>21</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:N5"/>
-  <sheetFormatPr defaultColWidth="8.71428571428571" defaultRowHeight="15" outlineLevelRow="4"/>
-  <cols>
-    <col min="1" max="1" width="17" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5714285714286" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.2857142857143" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.8571428571429" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.8571428571429" style="1" customWidth="1"/>
-    <col min="6" max="9" width="13.2857142857143" style="1" customWidth="1"/>
-    <col min="10" max="10" width="18" style="1" customWidth="1"/>
-    <col min="11" max="11" width="30" style="1" customWidth="1"/>
-    <col min="12" max="12" width="5.57142857142857" style="1" customWidth="1"/>
-    <col min="13" max="14" width="5.28571428571429" style="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:14">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/OurLib.xlsx
+++ b/OurLib.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12885" tabRatio="500" activeTab="2"/>
+    <workbookView windowWidth="28800" windowHeight="12885" tabRatio="500" firstSheet="10" activeTab="15"/>
   </bookViews>
   <sheets>
     <sheet name="01 - Резисторы" sheetId="1" r:id="rId1"/>
@@ -23,6 +23,7 @@
     <sheet name="14 - Кнопки" sheetId="13" r:id="rId14"/>
     <sheet name="15 - Моторы" sheetId="14" r:id="rId15"/>
     <sheet name="16 - Светодиоды" sheetId="15" r:id="rId16"/>
+    <sheet name="17 - Акустика" sheetId="17" r:id="rId17"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="223">
   <si>
     <t>Part Number</t>
   </si>
@@ -110,6 +111,12 @@
     <t>CompSMD.PcbLib</t>
   </si>
   <si>
+    <t>Переменный резистор</t>
+  </si>
+  <si>
+    <t>Resistor_M</t>
+  </si>
+  <si>
     <t>Конденсатор SMD</t>
   </si>
   <si>
@@ -206,490 +213,505 @@
     <t>DFN.PcbLib</t>
   </si>
   <si>
+    <t>MQ-131</t>
+  </si>
+  <si>
+    <t>Датчик воздуха</t>
+  </si>
+  <si>
+    <t>MQ (6)</t>
+  </si>
+  <si>
+    <t>Sensors.PcbLib</t>
+  </si>
+  <si>
+    <t>BQ24072RGTR</t>
+  </si>
+  <si>
+    <t>Контроллер заряда</t>
+  </si>
+  <si>
+    <t>Контроль заряда 1S</t>
+  </si>
+  <si>
+    <t>VQFN-16 (3X3)</t>
+  </si>
+  <si>
+    <t>ICs - Power.SchLib</t>
+  </si>
+  <si>
+    <t>XC6219</t>
+  </si>
+  <si>
+    <t>Стабилизатор</t>
+  </si>
+  <si>
+    <t>SOT-23-5</t>
+  </si>
+  <si>
+    <t>SOT.PcbLib</t>
+  </si>
+  <si>
+    <t>AMS1117</t>
+  </si>
+  <si>
+    <t>Линейный понижающий преобразователь</t>
+  </si>
+  <si>
+    <t>SOT-223-4</t>
+  </si>
+  <si>
+    <t>MT3608</t>
+  </si>
+  <si>
+    <t>Линейный повышающий преобразователь</t>
+  </si>
+  <si>
+    <t>SOT-23-6</t>
+  </si>
+  <si>
+    <t>TP4056</t>
+  </si>
+  <si>
+    <t>SOP-8</t>
+  </si>
+  <si>
+    <t>AP2112K</t>
+  </si>
+  <si>
+    <t>Bat</t>
+  </si>
+  <si>
+    <t>Источник питания</t>
+  </si>
+  <si>
+    <t>ATmega328P-AU</t>
+  </si>
+  <si>
+    <t>Микроконтроллеры</t>
+  </si>
+  <si>
+    <t>TQFP-32</t>
+  </si>
+  <si>
+    <t>ICs - MCUs.SchLib</t>
+  </si>
+  <si>
+    <t>Packages SMD.PcbLib</t>
+  </si>
+  <si>
+    <t>ESP32-U4WDH</t>
+  </si>
+  <si>
+    <t>QFN-48 (5x5)</t>
+  </si>
+  <si>
+    <t>ESP-WROOM-32</t>
+  </si>
+  <si>
+    <t>PCB_Modules.PcbLib</t>
+  </si>
+  <si>
+    <t>STM32F103C8T6</t>
+  </si>
+  <si>
+    <t>LQFP-48</t>
+  </si>
+  <si>
+    <t>NE555</t>
+  </si>
+  <si>
+    <t>Счетчик</t>
+  </si>
+  <si>
+    <t>555 таймер - счетчик</t>
+  </si>
+  <si>
+    <t>DIP-8</t>
+  </si>
+  <si>
+    <t>ICs - Logic.SchLib</t>
+  </si>
+  <si>
+    <t>DIP.PcbLib</t>
+  </si>
+  <si>
+    <t>К155ЛА3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Логический вентиль </t>
+  </si>
+  <si>
+    <t>4 Х 2И-НЕ</t>
+  </si>
+  <si>
+    <t>K155LA3</t>
+  </si>
+  <si>
+    <t>DIP-16</t>
+  </si>
+  <si>
+    <t>74HC00D</t>
+  </si>
+  <si>
+    <t>5 Х 2И-НЕ</t>
+  </si>
+  <si>
+    <t>SO-14</t>
+  </si>
+  <si>
+    <t>SO-Packages.PcbLib</t>
+  </si>
+  <si>
+    <t>OPA381</t>
+  </si>
+  <si>
+    <t>Усилитель</t>
+  </si>
+  <si>
+    <t>SOIC-8</t>
+  </si>
+  <si>
+    <t>PCF8574T</t>
+  </si>
+  <si>
+    <t>Расширитель GPIO</t>
+  </si>
+  <si>
+    <t>Расширитель GPIO по I2C</t>
+  </si>
+  <si>
+    <t>SOP-16</t>
+  </si>
+  <si>
+    <t>ICs - Interfaces.SchLib</t>
+  </si>
+  <si>
+    <t>Кварцевый Резонатор SMD</t>
+  </si>
+  <si>
+    <t>Кварцевый Резонатор</t>
+  </si>
+  <si>
+    <t>QR</t>
+  </si>
+  <si>
+    <t>QRSMD_3225</t>
+  </si>
+  <si>
+    <t>QR.SchLib</t>
+  </si>
+  <si>
+    <t>Диод</t>
+  </si>
+  <si>
+    <t>Diod</t>
+  </si>
+  <si>
+    <t>SOD-123FL</t>
+  </si>
+  <si>
+    <t>SOD-323FL</t>
+  </si>
+  <si>
+    <t>SOD-523FL</t>
+  </si>
+  <si>
+    <t>Diodes.SchLib</t>
+  </si>
+  <si>
+    <t>SOD.PcbLib</t>
+  </si>
+  <si>
+    <t>Диод Шоттки</t>
+  </si>
+  <si>
+    <t>Diod Shottki</t>
+  </si>
+  <si>
+    <t>Стабилитрон</t>
+  </si>
+  <si>
+    <t>Stabilitron</t>
+  </si>
+  <si>
+    <t>Сдвоенный диод</t>
+  </si>
+  <si>
+    <t>Diodx2</t>
+  </si>
+  <si>
+    <t>SOT-23-3</t>
+  </si>
+  <si>
+    <t>PNP Транзистор</t>
+  </si>
+  <si>
+    <t>Транзистор</t>
+  </si>
+  <si>
+    <t>PNPTransistor</t>
+  </si>
+  <si>
+    <t>Transistors.SchLib</t>
+  </si>
+  <si>
+    <t>NPN Транзистор</t>
+  </si>
+  <si>
+    <t>NPNTransistor</t>
+  </si>
+  <si>
+    <t>N Мосфет</t>
+  </si>
+  <si>
+    <t>NMOSFET</t>
+  </si>
+  <si>
+    <t>P Мосфет</t>
+  </si>
+  <si>
+    <t>PMOSFET</t>
+  </si>
+  <si>
+    <t>двойной N Мосфет</t>
+  </si>
+  <si>
+    <t>NMOSFETx2</t>
+  </si>
+  <si>
+    <t>TSOP-6</t>
+  </si>
+  <si>
+    <t>PROG UART</t>
+  </si>
+  <si>
+    <t>Спец. Разъем</t>
+  </si>
+  <si>
+    <t>Headers.SchLib</t>
+  </si>
+  <si>
+    <t>Headers.PcbLib</t>
+  </si>
+  <si>
+    <t>PROG SWD</t>
+  </si>
+  <si>
+    <t>USB Type-C 6pin</t>
+  </si>
+  <si>
+    <t>USB разъем</t>
+  </si>
+  <si>
+    <t>PLS-2.54-1</t>
+  </si>
+  <si>
+    <t>PLS разъем</t>
+  </si>
+  <si>
+    <t>PLS-2.54-S-1</t>
+  </si>
+  <si>
+    <t>PLS-2.54-N-1</t>
+  </si>
+  <si>
+    <t>PLS-2.54-2</t>
+  </si>
+  <si>
+    <t>PLS-2.54-S-2</t>
+  </si>
+  <si>
+    <t>PLS-2.54-N-2</t>
+  </si>
+  <si>
+    <t>PLS-2.54-3</t>
+  </si>
+  <si>
+    <t>PLS-2.54-S-3</t>
+  </si>
+  <si>
+    <t>PLS-2.54-N-3</t>
+  </si>
+  <si>
+    <t>PLS-2.54-4</t>
+  </si>
+  <si>
+    <t>PLS-2.54-S-4</t>
+  </si>
+  <si>
+    <t>PLS-2.54-N-4</t>
+  </si>
+  <si>
+    <t>PLS-2.54-5</t>
+  </si>
+  <si>
+    <t>PLS-2.54-S-5</t>
+  </si>
+  <si>
+    <t>PLS-2.54-N-5</t>
+  </si>
+  <si>
+    <t>PLS-2.54-6</t>
+  </si>
+  <si>
+    <t>PLS-2.54-S-6</t>
+  </si>
+  <si>
+    <t>PLS-2.54-N-6</t>
+  </si>
+  <si>
+    <t>PLS-1.27-1</t>
+  </si>
+  <si>
+    <t>PLS-1.27-N-1</t>
+  </si>
+  <si>
+    <t>PLS-1.27-F-1</t>
+  </si>
+  <si>
+    <t>PLS-1.27-2</t>
+  </si>
+  <si>
+    <t>PLS-1.27-N-2</t>
+  </si>
+  <si>
+    <t>PLS-1.27-F-2</t>
+  </si>
+  <si>
+    <t>PLS-1.27-3</t>
+  </si>
+  <si>
+    <t>PLS-1.27-N-3</t>
+  </si>
+  <si>
+    <t>PLS-1.27-F-3</t>
+  </si>
+  <si>
+    <t>PLS-1.27-4</t>
+  </si>
+  <si>
+    <t>PLS-1.27-N-4</t>
+  </si>
+  <si>
+    <t>PLS-1.27-F-4</t>
+  </si>
+  <si>
+    <t>PLS-1.27-5</t>
+  </si>
+  <si>
+    <t>PLS-1.27-N-5</t>
+  </si>
+  <si>
+    <t>PLS-1.27-F-5</t>
+  </si>
+  <si>
+    <t>PLS-1.27-6</t>
+  </si>
+  <si>
+    <t>PLS-1.27-N-6</t>
+  </si>
+  <si>
+    <t>PLS-1.27-F-6</t>
+  </si>
+  <si>
+    <t>Антенна</t>
+  </si>
+  <si>
+    <t>Antenna</t>
+  </si>
+  <si>
+    <t>Antennas.SchLib</t>
+  </si>
+  <si>
+    <t>Antennas.PcbLib</t>
+  </si>
+  <si>
+    <t>PCB MIFA</t>
+  </si>
+  <si>
+    <t>PCB MIFA MINI</t>
+  </si>
+  <si>
+    <t>Button</t>
+  </si>
+  <si>
+    <t>Кнопка</t>
+  </si>
+  <si>
+    <t>BUTTON 5.5x3</t>
+  </si>
+  <si>
+    <t>Switchers.SchLib</t>
+  </si>
+  <si>
+    <t>Switchers.PcbLib</t>
+  </si>
+  <si>
+    <t>Вибромотор PCB</t>
+  </si>
+  <si>
+    <t>Мотор</t>
+  </si>
+  <si>
+    <t>Vibromotor PCB</t>
+  </si>
+  <si>
+    <t>Vibromotor PCB 10 x 3.5 mm</t>
+  </si>
+  <si>
+    <t>Motors.SchLib</t>
+  </si>
+  <si>
+    <t>Motors.PcbLib</t>
+  </si>
+  <si>
+    <t>Светодиод SMD</t>
+  </si>
+  <si>
+    <t>Светодиод</t>
+  </si>
+  <si>
+    <t>LED</t>
+  </si>
+  <si>
+    <t>LED_0603</t>
+  </si>
+  <si>
+    <t>LED.SchLib</t>
+  </si>
+  <si>
+    <t>LEDs.PcbLib</t>
+  </si>
+  <si>
+    <t>BPW34</t>
+  </si>
+  <si>
+    <t>ИК- диод</t>
+  </si>
+  <si>
+    <t>Hinged_Diod</t>
+  </si>
+  <si>
+    <t>SFH 4550</t>
+  </si>
+  <si>
+    <t>Светодиод RGB</t>
+  </si>
+  <si>
+    <t>LED_RGB</t>
+  </si>
+  <si>
+    <t>Динамик</t>
+  </si>
+  <si>
+    <t>BA</t>
+  </si>
+  <si>
+    <t>BA.SchLib</t>
+  </si>
+  <si>
     <t>Buzzer</t>
-  </si>
-  <si>
-    <t>MQ-131</t>
-  </si>
-  <si>
-    <t>Датчик воздуха</t>
-  </si>
-  <si>
-    <t>MQ (6)</t>
-  </si>
-  <si>
-    <t>Sensors.PcbLib</t>
-  </si>
-  <si>
-    <t>BQ24072RGTR</t>
-  </si>
-  <si>
-    <t>Контроллер заряда</t>
-  </si>
-  <si>
-    <t>Контроль заряда 1S</t>
-  </si>
-  <si>
-    <t>VQFN-16 (3X3)</t>
-  </si>
-  <si>
-    <t>ICs - Power.SchLib</t>
-  </si>
-  <si>
-    <t>XC6219</t>
-  </si>
-  <si>
-    <t>Стабилизатор</t>
-  </si>
-  <si>
-    <t>SOT-23-5</t>
-  </si>
-  <si>
-    <t>SOT.PcbLib</t>
-  </si>
-  <si>
-    <t>AMS1117</t>
-  </si>
-  <si>
-    <t>Линейный понижающий преобразователь</t>
-  </si>
-  <si>
-    <t>SOT-223-4</t>
-  </si>
-  <si>
-    <t>MT3608</t>
-  </si>
-  <si>
-    <t>Линейный повышающий преобразователь</t>
-  </si>
-  <si>
-    <t>SOT-23-6</t>
-  </si>
-  <si>
-    <t>TP4056</t>
-  </si>
-  <si>
-    <t>SOP-8</t>
-  </si>
-  <si>
-    <t>AP2112K</t>
-  </si>
-  <si>
-    <t>ATmega328P-AU</t>
-  </si>
-  <si>
-    <t>Микроконтроллеры</t>
-  </si>
-  <si>
-    <t>TQFP-32</t>
-  </si>
-  <si>
-    <t>ICs - MCUs.SchLib</t>
-  </si>
-  <si>
-    <t>Packages SMD.PcbLib</t>
-  </si>
-  <si>
-    <t>ESP32-U4WDH</t>
-  </si>
-  <si>
-    <t>QFN-48 (5x5)</t>
-  </si>
-  <si>
-    <t>ESP-WROOM-32</t>
-  </si>
-  <si>
-    <t>PCB_Modules.PcbLib</t>
-  </si>
-  <si>
-    <t>STM32F103C8T6</t>
-  </si>
-  <si>
-    <t>LQFP-48</t>
-  </si>
-  <si>
-    <t>NE555</t>
-  </si>
-  <si>
-    <t>Счетчик</t>
-  </si>
-  <si>
-    <t>555 таймер - счетчик</t>
-  </si>
-  <si>
-    <t>DIP-8</t>
-  </si>
-  <si>
-    <t>ICs - Logic.SchLib</t>
-  </si>
-  <si>
-    <t>DIP.PcbLib</t>
-  </si>
-  <si>
-    <t>К155ЛА3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Логический вентиль </t>
-  </si>
-  <si>
-    <t>4 Х 2И-НЕ</t>
-  </si>
-  <si>
-    <t>K155LA3</t>
-  </si>
-  <si>
-    <t>DIP-16</t>
-  </si>
-  <si>
-    <t>74HC00D</t>
-  </si>
-  <si>
-    <t>5 Х 2И-НЕ</t>
-  </si>
-  <si>
-    <t>SO-14</t>
-  </si>
-  <si>
-    <t>SO-Packages.PcbLib</t>
-  </si>
-  <si>
-    <t>OPA381</t>
-  </si>
-  <si>
-    <t>Усилитель</t>
-  </si>
-  <si>
-    <t>SOIC-8</t>
-  </si>
-  <si>
-    <t>PCF8574T</t>
-  </si>
-  <si>
-    <t>Расширитель GPIO</t>
-  </si>
-  <si>
-    <t>Расширитель GPIO по I2C</t>
-  </si>
-  <si>
-    <t>SOP-16</t>
-  </si>
-  <si>
-    <t>ICs - Interfaces.SchLib</t>
-  </si>
-  <si>
-    <t>Кварцевый Резонатор SMD</t>
-  </si>
-  <si>
-    <t>Кварцевый Резонатор</t>
-  </si>
-  <si>
-    <t>QR</t>
-  </si>
-  <si>
-    <t>QRSMD_3225</t>
-  </si>
-  <si>
-    <t>QR.SchLib</t>
-  </si>
-  <si>
-    <t>Диод</t>
-  </si>
-  <si>
-    <t>Diod</t>
-  </si>
-  <si>
-    <t>SOD-123FL</t>
-  </si>
-  <si>
-    <t>SOD-323FL</t>
-  </si>
-  <si>
-    <t>SOD-523FL</t>
-  </si>
-  <si>
-    <t>Diodes.SchLib</t>
-  </si>
-  <si>
-    <t>SOD.PcbLib</t>
-  </si>
-  <si>
-    <t>Диод Шоттки</t>
-  </si>
-  <si>
-    <t>Diod Shottki</t>
-  </si>
-  <si>
-    <t>Стабилитрон</t>
-  </si>
-  <si>
-    <t>Stabilitron</t>
-  </si>
-  <si>
-    <t>Сдвоенный диод</t>
-  </si>
-  <si>
-    <t>Diodx2</t>
-  </si>
-  <si>
-    <t>SOT-23-3</t>
-  </si>
-  <si>
-    <t>PNP Транзистор</t>
-  </si>
-  <si>
-    <t>Транзистор</t>
-  </si>
-  <si>
-    <t>PNPTransistor</t>
-  </si>
-  <si>
-    <t>Transistors.SchLib</t>
-  </si>
-  <si>
-    <t>NPN Транзистор</t>
-  </si>
-  <si>
-    <t>NPNTransistor</t>
-  </si>
-  <si>
-    <t>N Мосфет</t>
-  </si>
-  <si>
-    <t>NMOSFET</t>
-  </si>
-  <si>
-    <t>P Мосфет</t>
-  </si>
-  <si>
-    <t>PMOSFET</t>
-  </si>
-  <si>
-    <t>двойной N Мосфет</t>
-  </si>
-  <si>
-    <t>NMOSFETx2</t>
-  </si>
-  <si>
-    <t>TSOP-6</t>
-  </si>
-  <si>
-    <t>PROG UART</t>
-  </si>
-  <si>
-    <t>Спец. Разъем</t>
-  </si>
-  <si>
-    <t>Headers.SchLib</t>
-  </si>
-  <si>
-    <t>Headers.PcbLib</t>
-  </si>
-  <si>
-    <t>PROG SWD</t>
-  </si>
-  <si>
-    <t>USB Type-C 6pin</t>
-  </si>
-  <si>
-    <t>USB разъем</t>
-  </si>
-  <si>
-    <t>PLS-2.54-1</t>
-  </si>
-  <si>
-    <t>PLS разъем</t>
-  </si>
-  <si>
-    <t>PLS-2.54-S-1</t>
-  </si>
-  <si>
-    <t>PLS-2.54-N-1</t>
-  </si>
-  <si>
-    <t>PLS-2.54-2</t>
-  </si>
-  <si>
-    <t>PLS-2.54-S-2</t>
-  </si>
-  <si>
-    <t>PLS-2.54-N-2</t>
-  </si>
-  <si>
-    <t>PLS-2.54-3</t>
-  </si>
-  <si>
-    <t>PLS-2.54-S-3</t>
-  </si>
-  <si>
-    <t>PLS-2.54-N-3</t>
-  </si>
-  <si>
-    <t>PLS-2.54-4</t>
-  </si>
-  <si>
-    <t>PLS-2.54-S-4</t>
-  </si>
-  <si>
-    <t>PLS-2.54-N-4</t>
-  </si>
-  <si>
-    <t>PLS-2.54-5</t>
-  </si>
-  <si>
-    <t>PLS-2.54-S-5</t>
-  </si>
-  <si>
-    <t>PLS-2.54-N-5</t>
-  </si>
-  <si>
-    <t>PLS-2.54-6</t>
-  </si>
-  <si>
-    <t>PLS-2.54-S-6</t>
-  </si>
-  <si>
-    <t>PLS-2.54-N-6</t>
-  </si>
-  <si>
-    <t>PLS-1.27-1</t>
-  </si>
-  <si>
-    <t>PLS-1.27-N-1</t>
-  </si>
-  <si>
-    <t>PLS-1.27-F-1</t>
-  </si>
-  <si>
-    <t>PLS-1.27-2</t>
-  </si>
-  <si>
-    <t>PLS-1.27-N-2</t>
-  </si>
-  <si>
-    <t>PLS-1.27-F-2</t>
-  </si>
-  <si>
-    <t>PLS-1.27-3</t>
-  </si>
-  <si>
-    <t>PLS-1.27-N-3</t>
-  </si>
-  <si>
-    <t>PLS-1.27-F-3</t>
-  </si>
-  <si>
-    <t>PLS-1.27-4</t>
-  </si>
-  <si>
-    <t>PLS-1.27-N-4</t>
-  </si>
-  <si>
-    <t>PLS-1.27-F-4</t>
-  </si>
-  <si>
-    <t>PLS-1.27-5</t>
-  </si>
-  <si>
-    <t>PLS-1.27-N-5</t>
-  </si>
-  <si>
-    <t>PLS-1.27-F-5</t>
-  </si>
-  <si>
-    <t>PLS-1.27-6</t>
-  </si>
-  <si>
-    <t>PLS-1.27-N-6</t>
-  </si>
-  <si>
-    <t>PLS-1.27-F-6</t>
-  </si>
-  <si>
-    <t>Антенна</t>
-  </si>
-  <si>
-    <t>Antenna</t>
-  </si>
-  <si>
-    <t>Antennas.SchLib</t>
-  </si>
-  <si>
-    <t>Antennas.PcbLib</t>
-  </si>
-  <si>
-    <t>PCB MIFA</t>
-  </si>
-  <si>
-    <t>PCB MIFA MINI</t>
-  </si>
-  <si>
-    <t>Button</t>
-  </si>
-  <si>
-    <t>Кнопка</t>
-  </si>
-  <si>
-    <t>BUTTON 5.5x3</t>
-  </si>
-  <si>
-    <t>Switchers.SchLib</t>
-  </si>
-  <si>
-    <t>Switchers.PcbLib</t>
-  </si>
-  <si>
-    <t>Вибромотор PCB</t>
-  </si>
-  <si>
-    <t>Мотор</t>
-  </si>
-  <si>
-    <t>Vibromotor PCB</t>
-  </si>
-  <si>
-    <t>Vibromotor PCB 10 x 3.5 mm</t>
-  </si>
-  <si>
-    <t>Motors.SchLib</t>
-  </si>
-  <si>
-    <t>Motors.PcbLib</t>
-  </si>
-  <si>
-    <t>Светодиод SMD</t>
-  </si>
-  <si>
-    <t>Светодиод</t>
-  </si>
-  <si>
-    <t>LED</t>
-  </si>
-  <si>
-    <t>LED_0603</t>
-  </si>
-  <si>
-    <t>LED.SchLib</t>
-  </si>
-  <si>
-    <t>LEDs.PcbLib</t>
-  </si>
-  <si>
-    <t>BPW34</t>
-  </si>
-  <si>
-    <t>ИК- диод</t>
-  </si>
-  <si>
-    <t>Hinged_Diod</t>
-  </si>
-  <si>
-    <t>SFH 4550</t>
-  </si>
-  <si>
-    <t>Светодиод RGB</t>
-  </si>
-  <si>
-    <t>LED_RGB</t>
   </si>
 </sst>
 </file>
@@ -1765,10 +1787,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultColWidth="8.71428571428571" defaultRowHeight="15" outlineLevelRow="1"/>
+  <dimension ref="A1:N3"/>
+  <sheetFormatPr defaultColWidth="8.71428571428571" defaultRowHeight="15" outlineLevelRow="2"/>
   <cols>
-    <col min="1" max="1" width="14.7142857142857" style="1" customWidth="1"/>
+    <col min="1" max="1" width="23" style="1" customWidth="1"/>
     <col min="2" max="2" width="19" style="1" customWidth="1"/>
     <col min="3" max="3" width="30.1428571428571" style="1" customWidth="1"/>
     <col min="4" max="4" width="13.2857142857143" style="1" customWidth="1"/>
@@ -1850,6 +1872,20 @@
       </c>
       <c r="K2" s="1" t="s">
         <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1923,100 +1959,100 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>121</v>
-      </c>
       <c r="K3" s="1" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>125</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -2090,102 +2126,102 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="J2" s="1" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>131</v>
-      </c>
       <c r="D3" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>133</v>
-      </c>
       <c r="K4" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="1" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -2262,338 +2298,338 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>144</v>
-      </c>
       <c r="D3" s="1" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>149</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="1" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>151</v>
-      </c>
       <c r="D6" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="1" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="1" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="1" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="1" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" s="1" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="1" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="1" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="1" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="1" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -2668,39 +2704,39 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="J3" s="1" t="s">
-        <v>189</v>
-      </c>
       <c r="K3" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
   </sheetData>
@@ -2775,22 +2811,22 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
     </row>
   </sheetData>
@@ -2861,22 +2897,22 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
   </sheetData>
@@ -2951,87 +2987,185 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="E3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>212</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="1" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="E4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>212</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="1" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:N3"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="2"/>
+  <cols>
+    <col min="1" max="1" width="15.7142857142857" customWidth="1"/>
+    <col min="2" max="2" width="19.4285714285714" customWidth="1"/>
+    <col min="3" max="3" width="17" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="10" max="10" width="20.1428571428571" customWidth="1"/>
+    <col min="11" max="11" width="15.7142857142857" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
+        <v>219</v>
+      </c>
+      <c r="D2" t="s">
+        <v>220</v>
+      </c>
+      <c r="J2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -3102,25 +3236,25 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>21</v>
@@ -3128,28 +3262,28 @@
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>21</v>
@@ -3222,19 +3356,19 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D2" t="s">
         <v>37</v>
       </c>
-      <c r="D2" t="s">
-        <v>35</v>
-      </c>
       <c r="J2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -3308,134 +3442,124 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="E2" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:14">
-      <c r="A6" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>53</v>
-      </c>
+      <c r="A6"/>
+      <c r="B6"/>
+      <c r="C6"/>
+      <c r="D6"/>
+      <c r="E6"/>
+      <c r="F6"/>
+      <c r="G6"/>
+      <c r="H6"/>
+      <c r="I6"/>
+      <c r="J6"/>
+      <c r="K6"/>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="E7" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -3448,8 +3572,8 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N7"/>
-  <sheetFormatPr defaultColWidth="8.71428571428571" defaultRowHeight="15" outlineLevelRow="6"/>
+  <dimension ref="A1:N8"/>
+  <sheetFormatPr defaultColWidth="8.71428571428571" defaultRowHeight="15" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="1" width="17.2857142857143" style="1" customWidth="1"/>
     <col min="2" max="2" width="19.5714285714286" style="1" customWidth="1"/>
@@ -3506,140 +3630,154 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>59</v>
-      </c>
       <c r="E2" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>63</v>
-      </c>
       <c r="K3" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>71</v>
-      </c>
       <c r="E5" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -3714,82 +3852,82 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="J3" s="1" t="s">
-        <v>80</v>
-      </c>
       <c r="K3" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -3865,94 +4003,94 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>92</v>
-      </c>
       <c r="K4" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="K5" s="1" t="s">
         <v>105</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -4023,25 +4161,25 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -4115,19 +4253,19 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>21</v>

--- a/OurLib.xlsx
+++ b/OurLib.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12885" tabRatio="500" firstSheet="10" activeTab="15"/>
+    <workbookView windowWidth="28800" windowHeight="12885" tabRatio="500" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="01 - Резисторы" sheetId="1" r:id="rId1"/>
@@ -156,13 +156,13 @@
     <t>CSMD_7343_P</t>
   </si>
   <si>
+    <t>Катушка индуктивности</t>
+  </si>
+  <si>
+    <t>Со стержнем</t>
+  </si>
+  <si>
     <t>Inductance coil</t>
-  </si>
-  <si>
-    <t>Катушка индуктивности</t>
-  </si>
-  <si>
-    <t>Со стержнем</t>
   </si>
   <si>
     <t>Inductance.SchLib</t>
@@ -3157,8 +3157,8 @@
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
-      <c r="J3" s="1" t="s">
-        <v>45</v>
+      <c r="J3" t="s">
+        <v>221</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>55</v>
@@ -3302,7 +3302,7 @@
   <dimension ref="A1:N2"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="16.5714285714286" customWidth="1"/>
+    <col min="1" max="1" width="22.2857142857143" customWidth="1"/>
     <col min="2" max="2" width="24.4285714285714" customWidth="1"/>
     <col min="3" max="3" width="18.8571428571429" customWidth="1"/>
     <col min="4" max="4" width="17.7142857142857" customWidth="1"/>
@@ -3359,13 +3359,13 @@
         <v>37</v>
       </c>
       <c r="B2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" t="s">
         <v>38</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>39</v>
-      </c>
-      <c r="D2" t="s">
-        <v>37</v>
       </c>
       <c r="J2" t="s">
         <v>40</v>
@@ -3380,8 +3380,8 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N7"/>
-  <sheetFormatPr defaultColWidth="8.71428571428571" defaultRowHeight="15" outlineLevelRow="6"/>
+  <dimension ref="A1:N6"/>
+  <sheetFormatPr defaultColWidth="8.71428571428571" defaultRowHeight="15" outlineLevelRow="5"/>
   <cols>
     <col min="1" max="1" width="22.4285714285714" style="1" customWidth="1"/>
     <col min="2" max="2" width="16.7142857142857" style="1" customWidth="1"/>
@@ -3527,38 +3527,25 @@
       </c>
     </row>
     <row r="6" spans="1:14">
-      <c r="A6"/>
-      <c r="B6"/>
-      <c r="C6"/>
-      <c r="D6"/>
-      <c r="E6"/>
-      <c r="F6"/>
-      <c r="G6"/>
-      <c r="H6"/>
-      <c r="I6"/>
-      <c r="J6"/>
-      <c r="K6"/>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="1" t="s">
+      <c r="A6" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B6" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C6" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="J6" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="K7" s="1" t="s">
+      <c r="K6" s="1" t="s">
         <v>59</v>
       </c>
     </row>

--- a/OurLib.xlsx
+++ b/OurLib.xlsx
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="223">
   <si>
     <t>Part Number</t>
   </si>
@@ -3306,6 +3306,7 @@
     <col min="2" max="2" width="24.4285714285714" customWidth="1"/>
     <col min="3" max="3" width="18.8571428571429" customWidth="1"/>
     <col min="4" max="4" width="17.7142857142857" customWidth="1"/>
+    <col min="5" max="5" width="12.5714285714286" customWidth="1"/>
     <col min="10" max="10" width="19.8571428571429" customWidth="1"/>
     <col min="11" max="11" width="17" customWidth="1"/>
   </cols>
@@ -3367,8 +3368,14 @@
       <c r="D2" t="s">
         <v>39</v>
       </c>
+      <c r="E2" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="J2" t="s">
         <v>40</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/OurLib.xlsx
+++ b/OurLib.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12885" tabRatio="500" activeTab="2"/>
+    <workbookView windowWidth="28800" windowHeight="12885" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="01 - Резисторы" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="224">
   <si>
     <t>Part Number</t>
   </si>
@@ -712,6 +712,9 @@
   </si>
   <si>
     <t>Buzzer</t>
+  </si>
+  <si>
+    <t>Acustic.PcbLib</t>
   </si>
 </sst>
 </file>
@@ -3161,7 +3164,7 @@
         <v>221</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>55</v>
+        <v>223</v>
       </c>
     </row>
   </sheetData>

--- a/OurLib.xlsx
+++ b/OurLib.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12885" tabRatio="500"/>
+    <workbookView windowWidth="28800" windowHeight="12285" tabRatio="500" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="01 - Резисторы" sheetId="1" r:id="rId1"/>
@@ -276,6 +276,9 @@
     <t>SOP-8</t>
   </si>
   <si>
+    <t>SO-Packages.PcbLib</t>
+  </si>
+  <si>
     <t>AP2112K</t>
   </si>
   <si>
@@ -358,9 +361,6 @@
   </si>
   <si>
     <t>SO-14</t>
-  </si>
-  <si>
-    <t>SO-Packages.PcbLib</t>
   </si>
   <si>
     <t>OPA381</t>
@@ -2224,7 +2224,7 @@
         <v>136</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>105</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -3737,12 +3737,12 @@
         <v>64</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>66</v>
@@ -3751,7 +3751,7 @@
         <v>66</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>67</v>
@@ -3765,13 +3765,13 @@
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>78</v>
       </c>
       <c r="J8" s="1" t="s">
         <v>64</v>
@@ -3849,39 +3849,39 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>80</v>
-      </c>
       <c r="E2" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>46</v>
@@ -3889,42 +3889,42 @@
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -4000,71 +4000,71 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>91</v>
-      </c>
       <c r="E2" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>102</v>
-      </c>
       <c r="E4" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>105</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -4084,10 +4084,10 @@
         <v>108</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>105</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -4176,7 +4176,7 @@
         <v>113</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>105</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/OurLib.xlsx
+++ b/OurLib.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ON_WORK\GitBin\Components Libs\my-altium-library\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FC21905-4960-48CD-9A47-9954C0BD1E0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12285" tabRatio="500" activeTab="4"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01 - Резисторы" sheetId="1" r:id="rId1"/>
@@ -34,8 +40,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -43,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="225">
   <si>
     <t>Part Number</t>
   </si>
@@ -435,12 +439,6 @@
     <t>Stabilitron</t>
   </si>
   <si>
-    <t>Сдвоенный диод</t>
-  </si>
-  <si>
-    <t>Diodx2</t>
-  </si>
-  <si>
     <t>SOT-23-3</t>
   </si>
   <si>
@@ -708,190 +706,37 @@
     <t>BA</t>
   </si>
   <si>
-    <t>BA.SchLib</t>
-  </si>
-  <si>
     <t>Buzzer</t>
   </si>
   <si>
     <t>Acustic.PcbLib</t>
+  </si>
+  <si>
+    <t>Diod x2 com 3</t>
+  </si>
+  <si>
+    <t>BAT54C</t>
+  </si>
+  <si>
+    <t>IRF2850</t>
+  </si>
+  <si>
+    <t>Sound Emmiters.SchLib</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="_-&quot;₽&quot;* #,##0.00_-;\-&quot;₽&quot;* #,##0.00_-;_-&quot;₽&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-* #,##0_-;\-&quot;₽&quot;* #,##0_-;_-&quot;₽&quot;* &quot;-&quot;_-;_-@_-"/>
-  </numFmts>
-  <fonts count="22">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="1"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="34">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -904,194 +749,8 @@
         <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1099,330 +758,167 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Запятая" xfId="1" builtinId="3"/>
-    <cellStyle name="Денежный" xfId="2" builtinId="4"/>
-    <cellStyle name="Процент" xfId="3" builtinId="5"/>
-    <cellStyle name="Запятая [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Денежный [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Гиперссылка" xfId="6" builtinId="8"/>
-    <cellStyle name="Открывавшаяся гиперссылка" xfId="7" builtinId="9"/>
-    <cellStyle name="Примечание" xfId="8" builtinId="10"/>
-    <cellStyle name="Предупреждающий текст" xfId="9" builtinId="11"/>
-    <cellStyle name="Заголовок" xfId="10" builtinId="15"/>
-    <cellStyle name="Пояснительный текст" xfId="11" builtinId="53"/>
-    <cellStyle name="Заголовок 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Заголовок 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Заголовок 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Заголовок 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Ввод" xfId="16" builtinId="20"/>
-    <cellStyle name="Вывод" xfId="17" builtinId="21"/>
-    <cellStyle name="Вычисление" xfId="18" builtinId="22"/>
-    <cellStyle name="Проверить ячейку" xfId="19" builtinId="23"/>
-    <cellStyle name="Связанная ячейка" xfId="20" builtinId="24"/>
-    <cellStyle name="Итого" xfId="21" builtinId="25"/>
-    <cellStyle name="Хороший" xfId="22" builtinId="26"/>
-    <cellStyle name="Плохой" xfId="23" builtinId="27"/>
-    <cellStyle name="Нейтральный" xfId="24" builtinId="28"/>
-    <cellStyle name="Акцент1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% — Акцент1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% — Акцент1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% — Акцент1" xfId="28" builtinId="32"/>
-    <cellStyle name="Акцент2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% — Акцент2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% — Акцент2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% — Акцент2" xfId="32" builtinId="36"/>
-    <cellStyle name="Акцент3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% — Акцент3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% — Акцент3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% — Акцент3" xfId="36" builtinId="40"/>
-    <cellStyle name="Акцент4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% — Акцент4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% — Акцент4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% — Акцент4" xfId="40" builtinId="44"/>
-    <cellStyle name="Акцент5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% — Акцент5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% — Акцент5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% — Акцент5" xfId="44" builtinId="48"/>
-    <cellStyle name="Акцент6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% — Акцент6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% — Акцент6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% — Акцент6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
       <border>
@@ -1433,7 +929,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="0"/>
       </font>
       <fill>
@@ -1461,154 +957,40 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.39994506668294322"/>
         </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="16"/>
+      <tableStyleElement type="headerRow" dxfId="15"/>
+      <tableStyleElement type="totalRow" dxfId="14"/>
+      <tableStyleElement type="firstColumn" dxfId="13"/>
+      <tableStyleElement type="lastColumn" dxfId="12"/>
+      <tableStyleElement type="firstRowStripe" dxfId="11"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="9"/>
+      <tableStyleElement type="totalRow" dxfId="8"/>
+      <tableStyleElement type="firstRowStripe" dxfId="7"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
+      <tableStyleElement type="pageFieldValues" dxfId="0"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1667,7 +1049,7 @@
         <a:cs typeface=""/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1784,30 +1166,30 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N3"/>
-  <sheetFormatPr defaultColWidth="8.71428571428571" defaultRowHeight="15" outlineLevelRow="2"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23" style="1" customWidth="1"/>
     <col min="2" max="2" width="19" style="1" customWidth="1"/>
-    <col min="3" max="3" width="30.1428571428571" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.2857142857143" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.4285714285714" style="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7142857142857" style="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5714285714286" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.7142857142857" style="1" customWidth="1"/>
-    <col min="9" max="9" width="14.4285714285714" style="1" customWidth="1"/>
-    <col min="10" max="10" width="15.7142857142857" style="1" customWidth="1"/>
-    <col min="11" max="11" width="29.8571428571429" style="1" customWidth="1"/>
-    <col min="12" max="12" width="8.42857142857143" style="1" customWidth="1"/>
+    <col min="3" max="3" width="30.109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.33203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.44140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14.6640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5546875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.6640625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="14.44140625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="15.6640625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="29.88671875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="8.44140625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1851,7 +1233,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -1877,7 +1259,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>22</v>
       </c>
@@ -1894,29 +1276,27 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:N5"/>
-  <sheetFormatPr defaultColWidth="8.71428571428571" defaultRowHeight="15" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5714285714286" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.2857142857143" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.8571428571429" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.8571428571429" style="1" customWidth="1"/>
-    <col min="6" max="9" width="13.2857142857143" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16.5546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.88671875" style="1" customWidth="1"/>
+    <col min="6" max="9" width="13.33203125" style="1" customWidth="1"/>
     <col min="10" max="10" width="18" style="1" customWidth="1"/>
     <col min="11" max="11" width="30" style="1" customWidth="1"/>
-    <col min="12" max="12" width="5.57142857142857" style="1" customWidth="1"/>
-    <col min="13" max="14" width="5.28571428571429" style="1" customWidth="1"/>
+    <col min="12" max="12" width="5.5546875" style="1" customWidth="1"/>
+    <col min="13" max="14" width="5.33203125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1960,7 +1340,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>119</v>
       </c>
@@ -1986,7 +1366,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>126</v>
       </c>
@@ -2012,7 +1392,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>128</v>
       </c>
@@ -2038,18 +1418,18 @@
         <v>125</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>130</v>
+        <v>222</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>119</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>131</v>
+        <v>221</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>124</v>
@@ -2061,29 +1441,27 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:N6"/>
-  <sheetFormatPr defaultColWidth="8.71428571428571" defaultRowHeight="15" outlineLevelRow="5"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28.8571428571429" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.2857142857143" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.2857142857143" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.7142857142857" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.7142857142857" style="1" customWidth="1"/>
-    <col min="6" max="9" width="13.2857142857143" style="1" customWidth="1"/>
-    <col min="10" max="10" width="22.1428571428571" style="1" customWidth="1"/>
-    <col min="11" max="11" width="29.5714285714286" style="1" customWidth="1"/>
-    <col min="12" max="12" width="5.57142857142857" style="1" customWidth="1"/>
-    <col min="13" max="14" width="5.28571428571429" style="1" customWidth="1"/>
+    <col min="1" max="1" width="28.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="28.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.33203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" style="1" customWidth="1"/>
+    <col min="6" max="9" width="13.33203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="22.109375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="29.5546875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="5.5546875" style="1" customWidth="1"/>
+    <col min="13" max="14" width="5.33203125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2127,101 +1505,104 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="E2" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="J2" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>136</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>136</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>136</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>136</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="J6" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>136</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>77</v>
@@ -2230,32 +1611,30 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:N16"/>
-  <sheetFormatPr defaultColWidth="8.71428571428571" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28.8571428571429" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18.5714285714286" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.2857142857143" style="1" customWidth="1"/>
-    <col min="4" max="4" width="18.7142857142857" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.7142857142857" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15.7142857142857" style="1" customWidth="1"/>
-    <col min="7" max="7" width="16.1428571428571" style="1" customWidth="1"/>
-    <col min="8" max="8" width="16.8571428571429" style="1" customWidth="1"/>
-    <col min="9" max="9" width="17.7142857142857" style="1" customWidth="1"/>
-    <col min="10" max="10" width="15.7142857142857" style="1" customWidth="1"/>
-    <col min="11" max="11" width="18.7142857142857" style="1" customWidth="1"/>
-    <col min="12" max="12" width="5.57142857142857" style="1" customWidth="1"/>
-    <col min="13" max="14" width="5.28571428571429" style="1" customWidth="1"/>
+    <col min="1" max="1" width="28.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.5546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15.6640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.109375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="16.88671875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="17.6640625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="15.6640625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="18.6640625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="5.5546875" style="1" customWidth="1"/>
+    <col min="13" max="14" width="5.33203125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2299,369 +1678,367 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="J2" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="D2" s="1" t="s">
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="K3" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="B3" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="1" t="s">
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B5" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E5" s="1" t="s">
+      <c r="J5" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="B6" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="J5" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="E6" s="1" t="s">
+      <c r="J6" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="B7" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="J6" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="E7" s="1" t="s">
+      <c r="J7" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="B8" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="J7" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="1" t="s">
+      <c r="F8" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="E8" s="1" t="s">
+      <c r="J8" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="B9" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="J8" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="1" t="s">
+      <c r="F9" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="E9" s="1" t="s">
+      <c r="J9" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="B10" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="J9" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="1" t="s">
+      <c r="F10" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="E10" s="1" t="s">
+      <c r="J10" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="B11" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="J10" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="1" t="s">
+      <c r="F11" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="J11" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="B12" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="J11" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="1" t="s">
+      <c r="F12" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="J12" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="B13" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="J12" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13" s="1" t="s">
+      <c r="F13" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="J13" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="B14" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="J13" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="A14" s="1" t="s">
+      <c r="F14" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="J14" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="B15" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="J14" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="A15" s="1" t="s">
+      <c r="F15" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="J15" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="B16" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="J15" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
-      <c r="A16" s="1" t="s">
+      <c r="F16" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>189</v>
-      </c>
       <c r="J16" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:N3"/>
-  <sheetFormatPr defaultColWidth="8.71428571428571" defaultRowHeight="15" outlineLevelRow="2"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.7142857142857" style="1" customWidth="1"/>
-    <col min="2" max="2" width="17.4285714285714" style="1" customWidth="1"/>
-    <col min="3" max="3" width="11.8571428571429" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.4285714285714" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.8571428571429" style="1" customWidth="1"/>
-    <col min="6" max="6" width="14.4285714285714" style="1" customWidth="1"/>
-    <col min="7" max="7" width="14.1428571428571" style="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5714285714286" style="1" customWidth="1"/>
-    <col min="9" max="9" width="17.1428571428571" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="17.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="11.88671875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.88671875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14.44140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14.109375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5546875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="17.109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="19" style="1" customWidth="1"/>
-    <col min="11" max="11" width="14.2857142857143" style="1" customWidth="1"/>
+    <col min="11" max="11" width="14.33203125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2705,70 +2082,68 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="J2" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="K2" s="1" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>191</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>193</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultColWidth="8.71428571428571" defaultRowHeight="15" outlineLevelRow="1"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.1428571428571" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.4285714285714" style="1" customWidth="1"/>
-    <col min="3" max="3" width="12.1428571428571" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.7142857142857" style="1" customWidth="1"/>
+    <col min="1" max="1" width="12.109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" style="1" customWidth="1"/>
     <col min="5" max="5" width="13" style="1" customWidth="1"/>
     <col min="6" max="6" width="15" style="1" customWidth="1"/>
-    <col min="7" max="7" width="15.2857142857143" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.1428571428571" style="1" customWidth="1"/>
-    <col min="9" max="9" width="15.2857142857143" style="1" customWidth="1"/>
-    <col min="10" max="10" width="15.5714285714286" style="1" customWidth="1"/>
-    <col min="11" max="11" width="18.1428571428571" style="1" customWidth="1"/>
+    <col min="7" max="7" width="15.33203125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.109375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.33203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="15.5546875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="18.109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2812,49 +2187,47 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="E2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>198</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>200</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultColWidth="8.71428571428571" defaultRowHeight="15" outlineLevelRow="1"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.2857142857143" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.7142857142857" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.1428571428571" style="1" customWidth="1"/>
-    <col min="4" max="4" width="18.4285714285714" style="1" customWidth="1"/>
-    <col min="5" max="5" width="27.8571428571429" style="1" customWidth="1"/>
-    <col min="10" max="10" width="19.7142857142857" style="1" customWidth="1"/>
-    <col min="11" max="11" width="18.1428571428571" style="1" customWidth="1"/>
+    <col min="1" max="1" width="18.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="27.88671875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="19.6640625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="18.109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2898,53 +2271,51 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>204</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>206</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:N5"/>
-  <sheetFormatPr defaultColWidth="8.71428571428571" defaultRowHeight="15" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.1428571428571" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.4285714285714" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.1428571428571" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.1428571428571" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.4285714285714" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15.1428571428571" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.7142857142857" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.2857142857143" style="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5714285714286" style="1" customWidth="1"/>
-    <col min="10" max="10" width="13.4285714285714" style="1" customWidth="1"/>
-    <col min="11" max="11" width="28.5714285714286" style="1" customWidth="1"/>
+    <col min="1" max="1" width="16.109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.44140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15.109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.6640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.33203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5546875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="13.44140625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="28.5546875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2988,108 +2359,106 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="J2" s="1" t="s">
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="1" t="s">
+      <c r="D3" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="J3" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="B4" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="J4" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="J3" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="1" t="s">
+      <c r="B5" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>218</v>
-      </c>
       <c r="J5" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:N3"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="2"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.7142857142857" customWidth="1"/>
-    <col min="2" max="2" width="19.4285714285714" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" customWidth="1"/>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
     <col min="3" max="3" width="17" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="10" max="10" width="20.1428571428571" customWidth="1"/>
-    <col min="11" max="11" width="15.7142857142857" customWidth="1"/>
+    <col min="10" max="10" width="20.109375" customWidth="1"/>
+    <col min="11" max="11" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3133,67 +2502,65 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D2" t="s">
+        <v>218</v>
+      </c>
+      <c r="J2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>219</v>
-      </c>
-      <c r="D2" t="s">
-        <v>220</v>
-      </c>
-      <c r="J2" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="1" t="s">
-        <v>222</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
       <c r="J3" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:N3"/>
-  <sheetFormatPr defaultColWidth="8.71428571428571" defaultRowHeight="15" outlineLevelRow="2"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.8571428571429" style="1" customWidth="1"/>
+    <col min="1" max="1" width="19.88671875" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" customWidth="1"/>
-    <col min="3" max="3" width="30.1428571428571" style="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7142857142857" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.4285714285714" style="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7142857142857" style="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5714285714286" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.7142857142857" style="1" customWidth="1"/>
-    <col min="9" max="9" width="14.4285714285714" style="1" customWidth="1"/>
-    <col min="10" max="10" width="17.7142857142857" style="1" customWidth="1"/>
-    <col min="11" max="11" width="35.8571428571429" style="1" customWidth="1"/>
-    <col min="12" max="12" width="8.42857142857143" style="1" customWidth="1"/>
+    <col min="3" max="3" width="30.109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.44140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14.6640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5546875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.6640625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="14.44140625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="17.6640625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="35.88671875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="8.44140625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3237,7 +2604,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>24</v>
       </c>
@@ -3263,7 +2630,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>31</v>
       </c>
@@ -3295,26 +2662,24 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="1"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.2857142857143" customWidth="1"/>
-    <col min="2" max="2" width="24.4285714285714" customWidth="1"/>
-    <col min="3" max="3" width="18.8571428571429" customWidth="1"/>
-    <col min="4" max="4" width="17.7142857142857" customWidth="1"/>
-    <col min="5" max="5" width="12.5714285714286" customWidth="1"/>
-    <col min="10" max="10" width="19.8571428571429" customWidth="1"/>
+    <col min="1" max="1" width="22.33203125" customWidth="1"/>
+    <col min="2" max="2" width="24.44140625" customWidth="1"/>
+    <col min="3" max="3" width="18.88671875" customWidth="1"/>
+    <col min="4" max="4" width="17.6640625" customWidth="1"/>
+    <col min="5" max="5" width="12.5546875" customWidth="1"/>
+    <col min="10" max="10" width="19.88671875" customWidth="1"/>
     <col min="11" max="11" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3358,7 +2723,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>37</v>
       </c>
@@ -3383,30 +2748,28 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:N6"/>
-  <sheetFormatPr defaultColWidth="8.71428571428571" defaultRowHeight="15" outlineLevelRow="5"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.4285714285714" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.7142857142857" style="1" customWidth="1"/>
-    <col min="3" max="3" width="26.7142857142857" style="1" customWidth="1"/>
-    <col min="4" max="4" width="18.4285714285714" style="1" customWidth="1"/>
+    <col min="1" max="1" width="22.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="26.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18.44140625" style="1" customWidth="1"/>
     <col min="5" max="5" width="15" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.7142857142857" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.1428571428571" style="1" customWidth="1"/>
-    <col min="8" max="8" width="13.8571428571429" style="1" customWidth="1"/>
-    <col min="9" max="9" width="12.7142857142857" style="1" customWidth="1"/>
-    <col min="10" max="10" width="19.2857142857143" style="1" customWidth="1"/>
-    <col min="11" max="11" width="27.5714285714286" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.6640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.109375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13.88671875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="12.6640625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="19.33203125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="27.5546875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3450,7 +2813,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>41</v>
       </c>
@@ -3473,7 +2836,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>47</v>
       </c>
@@ -3490,7 +2853,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>49</v>
       </c>
@@ -3513,7 +2876,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>52</v>
       </c>
@@ -3536,7 +2899,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>56</v>
       </c>
@@ -3562,26 +2925,24 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:N8"/>
-  <sheetFormatPr defaultColWidth="8.71428571428571" defaultRowHeight="15" outlineLevelRow="7"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.2857142857143" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.5714285714286" style="1" customWidth="1"/>
-    <col min="3" max="3" width="41.7142857142857" style="1" customWidth="1"/>
-    <col min="4" max="4" width="18.4285714285714" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.1428571428571" style="1" customWidth="1"/>
-    <col min="10" max="10" width="19.2857142857143" style="1" customWidth="1"/>
-    <col min="11" max="11" width="30.2857142857143" style="1" customWidth="1"/>
+    <col min="1" max="1" width="17.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="41.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.109375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="19.33203125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="30.33203125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3625,7 +2986,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>60</v>
       </c>
@@ -3648,7 +3009,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>65</v>
       </c>
@@ -3671,7 +3032,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>69</v>
       </c>
@@ -3694,7 +3055,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>72</v>
       </c>
@@ -3717,7 +3078,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>75</v>
       </c>
@@ -3740,7 +3101,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>78</v>
       </c>
@@ -3763,7 +3124,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>79</v>
       </c>
@@ -3780,30 +3141,28 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:N5"/>
-  <sheetFormatPr defaultColWidth="8.71428571428571" defaultRowHeight="15" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.4285714285714" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.4285714285714" style="1" customWidth="1"/>
-    <col min="3" max="3" width="26.7142857142857" style="1" customWidth="1"/>
-    <col min="4" max="4" width="18.4285714285714" style="1" customWidth="1"/>
+    <col min="1" max="1" width="22.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="26.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18.44140625" style="1" customWidth="1"/>
     <col min="5" max="5" width="15" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.7142857142857" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.1428571428571" style="1" customWidth="1"/>
-    <col min="8" max="8" width="13.8571428571429" style="1" customWidth="1"/>
-    <col min="9" max="9" width="12.7142857142857" style="1" customWidth="1"/>
-    <col min="10" max="10" width="19.2857142857143" style="1" customWidth="1"/>
-    <col min="11" max="11" width="24.2857142857143" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.6640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.109375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13.88671875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="12.6640625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="19.33203125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="24.33203125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3847,7 +3206,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>81</v>
       </c>
@@ -3867,7 +3226,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>86</v>
       </c>
@@ -3887,7 +3246,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>88</v>
       </c>
@@ -3907,7 +3266,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>90</v>
       </c>
@@ -3930,31 +3289,29 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:N5"/>
-  <sheetFormatPr defaultColWidth="8.71428571428571" defaultRowHeight="15" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.5714285714286" style="1" customWidth="1"/>
-    <col min="2" max="2" width="29.2857142857143" style="1" customWidth="1"/>
-    <col min="3" max="3" width="19.2857142857143" style="1" customWidth="1"/>
+    <col min="1" max="1" width="16.5546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="29.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" style="1" customWidth="1"/>
     <col min="4" max="4" width="15" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.1428571428571" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15.5714285714286" style="1" customWidth="1"/>
-    <col min="7" max="7" width="15.1428571428571" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.109375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15.5546875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="15.109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="14" style="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7142857142857" style="1" customWidth="1"/>
-    <col min="10" max="10" width="17.8571428571429" style="1" customWidth="1"/>
-    <col min="11" max="11" width="18.5714285714286" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.1428571428571" style="1" customWidth="1"/>
+    <col min="9" max="9" width="14.6640625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="17.88671875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="18.5546875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3998,7 +3355,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>92</v>
       </c>
@@ -4021,7 +3378,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>98</v>
       </c>
@@ -4044,7 +3401,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>103</v>
       </c>
@@ -4067,7 +3424,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>106</v>
       </c>
@@ -4093,26 +3450,24 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultColWidth="8.71428571428571" defaultRowHeight="15" outlineLevelRow="1"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.4285714285714" style="1" customWidth="1"/>
-    <col min="2" max="2" width="21.1428571428571" style="1" customWidth="1"/>
-    <col min="3" max="3" width="29.2857142857143" style="1" customWidth="1"/>
-    <col min="4" max="4" width="18.7142857142857" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.2857142857143" style="1" customWidth="1"/>
-    <col min="10" max="10" width="21.5714285714286" style="1" customWidth="1"/>
-    <col min="11" max="11" width="24.2857142857143" style="1" customWidth="1"/>
+    <col min="1" max="1" width="20.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="29.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="21.5546875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="24.33203125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4156,7 +3511,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>109</v>
       </c>
@@ -4182,29 +3537,27 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultColWidth="8.71428571428571" defaultRowHeight="15" outlineLevelRow="1"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.7142857142857" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20.2857142857143" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.2857142857143" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9.71428571428571" style="1" customWidth="1"/>
-    <col min="5" max="5" width="12.2857142857143" style="1" customWidth="1"/>
-    <col min="6" max="9" width="13.2857142857143" style="1" customWidth="1"/>
-    <col min="10" max="10" width="10.7142857142857" style="1" customWidth="1"/>
-    <col min="11" max="11" width="30.1428571428571" style="1" customWidth="1"/>
-    <col min="12" max="12" width="5.57142857142857" style="1" customWidth="1"/>
-    <col min="13" max="14" width="5.28571428571429" style="1" customWidth="1"/>
+    <col min="1" max="1" width="24.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="12.33203125" style="1" customWidth="1"/>
+    <col min="6" max="9" width="13.33203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.6640625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="30.109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="5.5546875" style="1" customWidth="1"/>
+    <col min="13" max="14" width="5.33203125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4248,7 +3601,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>114</v>
       </c>
@@ -4271,6 +3624,5 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/OurLib.xlsx
+++ b/OurLib.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ON_WORK\GitBin\Components Libs\my-altium-library\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FC21905-4960-48CD-9A47-9954C0BD1E0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="28800" windowHeight="12885" tabRatio="500" firstSheet="3" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="01 - Резисторы" sheetId="1" r:id="rId1"/>
@@ -40,6 +34,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -47,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="233">
   <si>
     <t>Part Number</t>
   </si>
@@ -292,6 +288,12 @@
     <t>Источник питания</t>
   </si>
   <si>
+    <t>USBLC6-2SC6</t>
+  </si>
+  <si>
+    <t>Защита питания</t>
+  </si>
+  <si>
     <t>ATmega328P-AU</t>
   </si>
   <si>
@@ -391,6 +393,24 @@
     <t>ICs - Interfaces.SchLib</t>
   </si>
   <si>
+    <t>ADS1115</t>
+  </si>
+  <si>
+    <t>АЦП</t>
+  </si>
+  <si>
+    <t>X2QFN-10</t>
+  </si>
+  <si>
+    <t>CP2102</t>
+  </si>
+  <si>
+    <t>USB-UART</t>
+  </si>
+  <si>
+    <t>QFN-28 (7x7)</t>
+  </si>
+  <si>
     <t>Кварцевый Резонатор SMD</t>
   </si>
   <si>
@@ -439,6 +459,12 @@
     <t>Stabilitron</t>
   </si>
   <si>
+    <t>BAT54C</t>
+  </si>
+  <si>
+    <t>Diod x2 com 3</t>
+  </si>
+  <si>
     <t>SOT-23-3</t>
   </si>
   <si>
@@ -472,6 +498,9 @@
     <t>PMOSFET</t>
   </si>
   <si>
+    <t>IRF2850</t>
+  </si>
+  <si>
     <t>двойной N Мосфет</t>
   </si>
   <si>
@@ -706,37 +735,185 @@
     <t>BA</t>
   </si>
   <si>
+    <t>Sound Emmiters.SchLib</t>
+  </si>
+  <si>
     <t>Buzzer</t>
   </si>
   <si>
     <t>Acustic.PcbLib</t>
-  </si>
-  <si>
-    <t>Diod x2 com 3</t>
-  </si>
-  <si>
-    <t>BAT54C</t>
-  </si>
-  <si>
-    <t>IRF2850</t>
-  </si>
-  <si>
-    <t>Sound Emmiters.SchLib</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-* #,##0.00\ &quot;₽&quot;_-;\-* #,##0.00\ &quot;₽&quot;_-;_-* &quot;-&quot;??\ &quot;₽&quot;_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-* #,##0\ &quot;₽&quot;_-;\-* #,##0\ &quot;₽&quot;_-;_-* &quot;-&quot;\ &quot;₽&quot;_-;_-@_-"/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -749,8 +926,194 @@
         <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -758,167 +1121,340 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Запятая" xfId="1" builtinId="3"/>
+    <cellStyle name="Денежный" xfId="2" builtinId="4"/>
+    <cellStyle name="Процент" xfId="3" builtinId="5"/>
+    <cellStyle name="Запятая [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Денежный [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Гиперссылка" xfId="6" builtinId="8"/>
+    <cellStyle name="Открывавшаяся гиперссылка" xfId="7" builtinId="9"/>
+    <cellStyle name="Примечание" xfId="8" builtinId="10"/>
+    <cellStyle name="Предупреждающий текст" xfId="9" builtinId="11"/>
+    <cellStyle name="Заголовок" xfId="10" builtinId="15"/>
+    <cellStyle name="Пояснительный текст" xfId="11" builtinId="53"/>
+    <cellStyle name="Заголовок 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Заголовок 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Заголовок 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Заголовок 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Ввод" xfId="16" builtinId="20"/>
+    <cellStyle name="Вывод" xfId="17" builtinId="21"/>
+    <cellStyle name="Вычисление" xfId="18" builtinId="22"/>
+    <cellStyle name="Проверить ячейку" xfId="19" builtinId="23"/>
+    <cellStyle name="Связанная ячейка" xfId="20" builtinId="24"/>
+    <cellStyle name="Итого" xfId="21" builtinId="25"/>
+    <cellStyle name="Хороший" xfId="22" builtinId="26"/>
+    <cellStyle name="Плохой" xfId="23" builtinId="27"/>
+    <cellStyle name="Нейтральный" xfId="24" builtinId="28"/>
+    <cellStyle name="Акцент1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% — Акцент1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% — Акцент1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% — Акцент1" xfId="28" builtinId="32"/>
+    <cellStyle name="Акцент2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% — Акцент2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% — Акцент2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% — Акцент2" xfId="32" builtinId="36"/>
+    <cellStyle name="Акцент3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% — Акцент3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% — Акцент3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% — Акцент3" xfId="36" builtinId="40"/>
+    <cellStyle name="Акцент4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% — Акцент4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% — Акцент4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% — Акцент4" xfId="40" builtinId="44"/>
+    <cellStyle name="Акцент5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% — Акцент5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% — Акцент5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% — Акцент5" xfId="44" builtinId="48"/>
+    <cellStyle name="Акцент6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% — Акцент6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% — Акцент6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% — Акцент6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
       <border>
@@ -929,7 +1465,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="0"/>
       </font>
       <fill>
@@ -957,40 +1493,154 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
+          <color theme="4" tint="0.399975585192419"/>
         </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="16"/>
-      <tableStyleElement type="headerRow" dxfId="15"/>
-      <tableStyleElement type="totalRow" dxfId="14"/>
-      <tableStyleElement type="firstColumn" dxfId="13"/>
-      <tableStyleElement type="lastColumn" dxfId="12"/>
-      <tableStyleElement type="firstRowStripe" dxfId="11"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="9"/>
-      <tableStyleElement type="totalRow" dxfId="8"/>
-      <tableStyleElement type="firstRowStripe" dxfId="7"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
-      <tableStyleElement type="pageFieldValues" dxfId="0"/>
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1049,7 +1699,7 @@
         <a:cs typeface=""/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme>
+    <a:fmtScheme name="">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1166,30 +1816,30 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:N3"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="15" outlineLevelRow="2"/>
   <cols>
     <col min="1" max="1" width="23" style="1" customWidth="1"/>
     <col min="2" max="2" width="19" style="1" customWidth="1"/>
-    <col min="3" max="3" width="30.109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.33203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.44140625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="14.6640625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5546875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.6640625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="14.44140625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="15.6640625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="29.88671875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="8.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="30.1047619047619" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.3333333333333" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.4380952380952" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14.6666666666667" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14.552380952381" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.6666666666667" style="1" customWidth="1"/>
+    <col min="9" max="9" width="14.4380952380952" style="1" customWidth="1"/>
+    <col min="10" max="10" width="15.6666666666667" style="1" customWidth="1"/>
+    <col min="11" max="11" width="29.8857142857143" style="1" customWidth="1"/>
+    <col min="12" max="12" width="8.43809523809524" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1233,7 +1883,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -1259,7 +1909,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
         <v>22</v>
       </c>
@@ -1276,27 +1926,29 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:N5"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
     <col min="1" max="1" width="17" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.33203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="16.5546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.88671875" style="1" customWidth="1"/>
-    <col min="6" max="9" width="13.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.552380952381" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.3333333333333" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16.552380952381" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.8857142857143" style="1" customWidth="1"/>
+    <col min="6" max="9" width="13.3333333333333" style="1" customWidth="1"/>
     <col min="10" max="10" width="18" style="1" customWidth="1"/>
     <col min="11" max="11" width="30" style="1" customWidth="1"/>
-    <col min="12" max="12" width="5.5546875" style="1" customWidth="1"/>
-    <col min="13" max="14" width="5.33203125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="5.55238095238095" style="1" customWidth="1"/>
+    <col min="13" max="14" width="5.33333333333333" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1340,99 +1992,99 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>119</v>
-      </c>
       <c r="D5" s="1" t="s">
-        <v>221</v>
+        <v>139</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>68</v>
@@ -1441,27 +2093,29 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:N6"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="15" outlineLevelRow="5"/>
   <cols>
-    <col min="1" max="1" width="28.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.33203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="28.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.33203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.6640625" style="1" customWidth="1"/>
-    <col min="6" max="9" width="13.33203125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="22.109375" style="1" customWidth="1"/>
-    <col min="11" max="11" width="29.5546875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="5.5546875" style="1" customWidth="1"/>
-    <col min="13" max="14" width="5.33203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="28.8857142857143" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.3333333333333" style="1" customWidth="1"/>
+    <col min="3" max="3" width="28.6666666666667" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.3333333333333" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.6666666666667" style="1" customWidth="1"/>
+    <col min="6" max="9" width="13.3333333333333" style="1" customWidth="1"/>
+    <col min="10" max="10" width="22.1047619047619" style="1" customWidth="1"/>
+    <col min="11" max="11" width="29.552380952381" style="1" customWidth="1"/>
+    <col min="12" max="12" width="5.55238095238095" style="1" customWidth="1"/>
+    <col min="13" max="14" width="5.33333333333333" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1505,104 +2159,104 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14">
       <c r="A4" s="1" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14">
       <c r="A5" s="1" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>130</v>
-      </c>
       <c r="J5" s="1" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14">
       <c r="A6" s="1" t="s">
-        <v>223</v>
+        <v>151</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>77</v>
@@ -1611,30 +2265,32 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:N16"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="28.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18.5546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.33203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="18.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.6640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15.6640625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="16.109375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="16.88671875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="17.6640625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="15.6640625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="18.6640625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="5.5546875" style="1" customWidth="1"/>
-    <col min="13" max="14" width="5.33203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="28.8857142857143" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.552380952381" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.3333333333333" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18.6666666666667" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.6666666666667" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15.6666666666667" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.1047619047619" style="1" customWidth="1"/>
+    <col min="8" max="8" width="16.8857142857143" style="1" customWidth="1"/>
+    <col min="9" max="9" width="17.6666666666667" style="1" customWidth="1"/>
+    <col min="10" max="10" width="15.6666666666667" style="1" customWidth="1"/>
+    <col min="11" max="11" width="18.6666666666667" style="1" customWidth="1"/>
+    <col min="12" max="12" width="5.55238095238095" style="1" customWidth="1"/>
+    <col min="13" max="14" width="5.33333333333333" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1678,367 +2334,369 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="1" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="1" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" s="1" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="F6" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="J6" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="J6" s="1" t="s">
-        <v>146</v>
-      </c>
       <c r="K6" s="1" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="K7" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="D7" s="1" t="s">
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="K8" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="F8" s="1" t="s">
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="J8" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>152</v>
-      </c>
       <c r="D9" s="1" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" s="1" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" s="1" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" s="1" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" s="1" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" s="1" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" s="1" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" s="1" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:N3"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="15" outlineLevelRow="2"/>
   <cols>
-    <col min="1" max="1" width="13.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="17.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="11.88671875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.88671875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="14.44140625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="14.109375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5546875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="17.109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.6666666666667" style="1" customWidth="1"/>
+    <col min="2" max="2" width="17.4380952380952" style="1" customWidth="1"/>
+    <col min="3" max="3" width="11.8857142857143" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.4380952380952" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.8857142857143" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14.4380952380952" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14.1047619047619" style="1" customWidth="1"/>
+    <col min="8" max="8" width="14.552380952381" style="1" customWidth="1"/>
+    <col min="9" max="9" width="17.1047619047619" style="1" customWidth="1"/>
     <col min="10" max="10" width="19" style="1" customWidth="1"/>
-    <col min="11" max="11" width="14.33203125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="14.3333333333333" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2082,68 +2740,70 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="12.109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="12.109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.6640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1047619047619" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.4380952380952" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.1047619047619" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.6666666666667" style="1" customWidth="1"/>
     <col min="5" max="5" width="13" style="1" customWidth="1"/>
     <col min="6" max="6" width="15" style="1" customWidth="1"/>
-    <col min="7" max="7" width="15.33203125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.109375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="15.33203125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="15.5546875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="18.109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="15.3333333333333" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.1047619047619" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.3333333333333" style="1" customWidth="1"/>
+    <col min="10" max="10" width="15.552380952381" style="1" customWidth="1"/>
+    <col min="11" max="11" width="18.1047619047619" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2187,47 +2847,49 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="18.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="18.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="27.88671875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="19.6640625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="18.109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="18.3333333333333" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.6666666666667" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.1047619047619" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18.4380952380952" style="1" customWidth="1"/>
+    <col min="5" max="5" width="27.8857142857143" style="1" customWidth="1"/>
+    <col min="10" max="10" width="19.6666666666667" style="1" customWidth="1"/>
+    <col min="11" max="11" width="18.1047619047619" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2271,51 +2933,53 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:N5"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="16.109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.44140625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15.109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.6640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.33203125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5546875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="13.44140625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="28.5546875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="16.1047619047619" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.4380952380952" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.1047619047619" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.1047619047619" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.4380952380952" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15.1047619047619" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.6666666666667" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.3333333333333" style="1" customWidth="1"/>
+    <col min="9" max="9" width="14.552380952381" style="1" customWidth="1"/>
+    <col min="10" max="10" width="13.4380952380952" style="1" customWidth="1"/>
+    <col min="11" max="11" width="28.552380952381" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2359,106 +3023,108 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="1" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="1" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>210</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:N3"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.1047619047619" defaultRowHeight="15" outlineLevelRow="2"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" customWidth="1"/>
-    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="1" max="1" width="15.6666666666667" customWidth="1"/>
+    <col min="2" max="2" width="19.4380952380952" customWidth="1"/>
     <col min="3" max="3" width="17" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="10" max="10" width="20.109375" customWidth="1"/>
-    <col min="11" max="11" width="15.6640625" customWidth="1"/>
+    <col min="10" max="10" width="20.1047619047619" customWidth="1"/>
+    <col min="11" max="11" width="15.6666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2502,65 +3168,67 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="D2" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="J2" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
       <c r="J3" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:N3"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="15" outlineLevelRow="2"/>
   <cols>
-    <col min="1" max="1" width="19.88671875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="19.8857142857143" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" customWidth="1"/>
-    <col min="3" max="3" width="30.109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="14.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.44140625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="14.6640625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5546875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.6640625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="14.44140625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="17.6640625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="35.88671875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="8.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="30.1047619047619" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14.6666666666667" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.4380952380952" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14.6666666666667" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14.552380952381" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.6666666666667" style="1" customWidth="1"/>
+    <col min="9" max="9" width="14.4380952380952" style="1" customWidth="1"/>
+    <col min="10" max="10" width="17.6666666666667" style="1" customWidth="1"/>
+    <col min="11" max="11" width="35.8857142857143" style="1" customWidth="1"/>
+    <col min="12" max="12" width="8.43809523809524" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2604,7 +3272,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
         <v>24</v>
       </c>
@@ -2630,7 +3298,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
         <v>31</v>
       </c>
@@ -2662,24 +3330,26 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.1047619047619" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="22.33203125" customWidth="1"/>
-    <col min="2" max="2" width="24.44140625" customWidth="1"/>
-    <col min="3" max="3" width="18.88671875" customWidth="1"/>
-    <col min="4" max="4" width="17.6640625" customWidth="1"/>
-    <col min="5" max="5" width="12.5546875" customWidth="1"/>
-    <col min="10" max="10" width="19.88671875" customWidth="1"/>
+    <col min="1" max="1" width="22.3333333333333" customWidth="1"/>
+    <col min="2" max="2" width="24.4380952380952" customWidth="1"/>
+    <col min="3" max="3" width="18.8857142857143" customWidth="1"/>
+    <col min="4" max="4" width="17.6666666666667" customWidth="1"/>
+    <col min="5" max="5" width="12.552380952381" customWidth="1"/>
+    <col min="10" max="10" width="19.8857142857143" customWidth="1"/>
     <col min="11" max="11" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2723,7 +3393,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
         <v>37</v>
       </c>
@@ -2748,28 +3418,30 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:N6"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="15" outlineLevelRow="5"/>
   <cols>
-    <col min="1" max="1" width="22.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="26.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="18.44140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="22.4380952380952" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.6666666666667" style="1" customWidth="1"/>
+    <col min="3" max="3" width="26.6666666666667" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18.4380952380952" style="1" customWidth="1"/>
     <col min="5" max="5" width="15" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.6640625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.109375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="13.88671875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="12.6640625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="19.33203125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="27.5546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.6666666666667" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.1047619047619" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13.8857142857143" style="1" customWidth="1"/>
+    <col min="9" max="9" width="12.6666666666667" style="1" customWidth="1"/>
+    <col min="10" max="10" width="19.3333333333333" style="1" customWidth="1"/>
+    <col min="11" max="11" width="27.552380952381" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2813,7 +3485,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
         <v>41</v>
       </c>
@@ -2836,7 +3508,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
         <v>47</v>
       </c>
@@ -2853,7 +3525,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14">
       <c r="A4" s="1" t="s">
         <v>49</v>
       </c>
@@ -2876,7 +3548,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14">
       <c r="A5" s="1" t="s">
         <v>52</v>
       </c>
@@ -2899,7 +3571,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14">
       <c r="A6" s="1" t="s">
         <v>56</v>
       </c>
@@ -2925,24 +3597,26 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:N8"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:N9"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="17.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.5546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="41.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="18.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.109375" style="1" customWidth="1"/>
-    <col min="10" max="10" width="19.33203125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="30.33203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="17.3333333333333" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.552380952381" style="1" customWidth="1"/>
+    <col min="3" max="3" width="41.6666666666667" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18.4380952380952" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.1047619047619" style="1" customWidth="1"/>
+    <col min="10" max="10" width="19.3333333333333" style="1" customWidth="1"/>
+    <col min="11" max="11" width="30.3333333333333" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2986,7 +3660,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
         <v>60</v>
       </c>
@@ -3009,7 +3683,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
         <v>65</v>
       </c>
@@ -3032,7 +3706,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14">
       <c r="A4" s="1" t="s">
         <v>69</v>
       </c>
@@ -3055,7 +3729,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14">
       <c r="A5" s="1" t="s">
         <v>72</v>
       </c>
@@ -3078,7 +3752,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14">
       <c r="A6" s="1" t="s">
         <v>75</v>
       </c>
@@ -3101,7 +3775,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14">
       <c r="A7" s="1" t="s">
         <v>78</v>
       </c>
@@ -3124,7 +3798,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14">
       <c r="A8" s="1" t="s">
         <v>79</v>
       </c>
@@ -3136,33 +3810,55 @@
       </c>
       <c r="J8" s="1" t="s">
         <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:N5"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="22.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="26.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="18.44140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="22.4380952380952" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.4380952380952" style="1" customWidth="1"/>
+    <col min="3" max="3" width="26.6666666666667" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18.4380952380952" style="1" customWidth="1"/>
     <col min="5" max="5" width="15" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.6640625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.109375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="13.88671875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="12.6640625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="19.33203125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="24.33203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.6666666666667" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.1047619047619" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13.8857142857143" style="1" customWidth="1"/>
+    <col min="9" max="9" width="12.6666666666667" style="1" customWidth="1"/>
+    <col min="10" max="10" width="19.3333333333333" style="1" customWidth="1"/>
+    <col min="11" max="11" width="24.3333333333333" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3206,112 +3902,114 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="J2" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="D3" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>86</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>84</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14">
       <c r="A4" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="J4" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="K4" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>82</v>
-      </c>
       <c r="D5" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:N5"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="16.5546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="29.33203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="16.552380952381" style="1" customWidth="1"/>
+    <col min="2" max="2" width="29.3333333333333" style="1" customWidth="1"/>
+    <col min="3" max="3" width="19.3333333333333" style="1" customWidth="1"/>
     <col min="4" max="4" width="15" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15.5546875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="15.109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.1047619047619" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15.552380952381" style="1" customWidth="1"/>
+    <col min="7" max="7" width="15.1047619047619" style="1" customWidth="1"/>
     <col min="8" max="8" width="14" style="1" customWidth="1"/>
-    <col min="9" max="9" width="14.6640625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="17.88671875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="18.5546875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.109375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="14.6666666666667" style="1" customWidth="1"/>
+    <col min="10" max="10" width="17.8857142857143" style="1" customWidth="1"/>
+    <col min="11" max="11" width="18.552380952381" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.1047619047619" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3355,93 +4053,93 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>92</v>
-      </c>
       <c r="E2" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D3" s="1" t="s">
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>99</v>
-      </c>
       <c r="C4" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14">
       <c r="A5" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>77</v>
@@ -3450,24 +4148,26 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:N4"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="15" outlineLevelRow="3"/>
   <cols>
-    <col min="1" max="1" width="20.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="21.109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="29.33203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="18.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.33203125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="21.5546875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="24.33203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="20.4380952380952" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.1047619047619" style="1" customWidth="1"/>
+    <col min="3" max="3" width="29.3333333333333" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18.6666666666667" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.3333333333333" style="1" customWidth="1"/>
+    <col min="10" max="10" width="21.552380952381" style="1" customWidth="1"/>
+    <col min="11" max="11" width="24.3333333333333" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3511,53 +4211,95 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>109</v>
-      </c>
       <c r="E2" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="24.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20.33203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.33203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="12.33203125" style="1" customWidth="1"/>
-    <col min="6" max="9" width="13.33203125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="10.6640625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="30.109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="5.5546875" style="1" customWidth="1"/>
-    <col min="13" max="14" width="5.33203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="24.6666666666667" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.3333333333333" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.3333333333333" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9.66666666666667" style="1" customWidth="1"/>
+    <col min="5" max="5" width="12.3333333333333" style="1" customWidth="1"/>
+    <col min="6" max="9" width="13.3333333333333" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.6666666666667" style="1" customWidth="1"/>
+    <col min="11" max="11" width="30.1047619047619" style="1" customWidth="1"/>
+    <col min="12" max="12" width="5.55238095238095" style="1" customWidth="1"/>
+    <col min="13" max="14" width="5.33333333333333" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3601,21 +4343,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>21</v>
@@ -3624,5 +4366,6 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/OurLib.xlsx
+++ b/OurLib.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12885" tabRatio="500" firstSheet="3" activeTab="4"/>
+    <workbookView windowWidth="28800" windowHeight="12885" tabRatio="500" firstSheet="3" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="01 - Резисторы" sheetId="1" r:id="rId1"/>
@@ -408,7 +408,7 @@
     <t>USB-UART</t>
   </si>
   <si>
-    <t>QFN-28 (7x7)</t>
+    <t>QFN-28 (5x5)</t>
   </si>
   <si>
     <t>Кварцевый Резонатор SMD</t>

--- a/OurLib.xlsx
+++ b/OurLib.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12885" tabRatio="500" firstSheet="3" activeTab="7"/>
+    <workbookView windowWidth="28800" windowHeight="12885" tabRatio="500" firstSheet="2" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="01 - Резисторы" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="243">
   <si>
     <t>Part Number</t>
   </si>
@@ -294,6 +294,21 @@
     <t>Защита питания</t>
   </si>
   <si>
+    <t>TPS7A20</t>
+  </si>
+  <si>
+    <t>Стабилизатор напряжения</t>
+  </si>
+  <si>
+    <t>SOT-563</t>
+  </si>
+  <si>
+    <t>TPS61023</t>
+  </si>
+  <si>
+    <t>Повышающий преобразователь</t>
+  </si>
+  <si>
     <t>ATmega328P-AU</t>
   </si>
   <si>
@@ -378,6 +393,12 @@
     <t>SOIC-8</t>
   </si>
   <si>
+    <t>Footprint Path 2</t>
+  </si>
+  <si>
+    <t>Footprint Path 3</t>
+  </si>
+  <si>
     <t>PCF8574T</t>
   </si>
   <si>
@@ -409,6 +430,15 @@
   </si>
   <si>
     <t>QFN-28 (5x5)</t>
+  </si>
+  <si>
+    <t>74HC595</t>
+  </si>
+  <si>
+    <t>Сдвиговый регистр</t>
+  </si>
+  <si>
+    <t>DHVQFN16</t>
   </si>
   <si>
     <t>Кварцевый Резонатор SMD</t>
@@ -1994,97 +2024,97 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="1" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="1" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>68</v>
@@ -2161,19 +2191,19 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>68</v>
@@ -2181,19 +2211,19 @@
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>68</v>
@@ -2201,19 +2231,19 @@
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="1" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>68</v>
@@ -2221,19 +2251,19 @@
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="1" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>140</v>
-      </c>
       <c r="J5" s="1" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>68</v>
@@ -2241,22 +2271,22 @@
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="1" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="J6" s="1" t="s">
         <v>154</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>144</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>77</v>
@@ -2336,338 +2366,338 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="1" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="1" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="1" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="J6" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="K6" s="1" t="s">
         <v>168</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="1" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="1" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="1" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="1" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="1" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" s="1" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="1" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="1" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="1" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="1" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -2742,39 +2772,39 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
     </row>
   </sheetData>
@@ -2849,22 +2879,22 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
     </row>
   </sheetData>
@@ -2935,22 +2965,22 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
     </row>
   </sheetData>
@@ -3025,82 +3055,82 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="1" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
     </row>
   </sheetData>
@@ -3170,36 +3200,36 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="D2" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="J2" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
       <c r="J3" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
     </row>
   </sheetData>
@@ -3604,7 +3634,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.3333333333333" style="1" customWidth="1"/>
@@ -3829,6 +3859,46 @@
         <v>64</v>
       </c>
       <c r="K9" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="K11" s="1" t="s">
         <v>68</v>
       </c>
     </row>
@@ -3904,39 +3974,39 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>46</v>
@@ -3944,42 +4014,42 @@
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="1" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="K5" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -4055,68 +4125,68 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>104</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="1" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>77</v>
@@ -4124,22 +4194,22 @@
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="1" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>77</v>
@@ -4155,19 +4225,23 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N4"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="15" outlineLevelRow="3"/>
+  <dimension ref="A1:P5"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
     <col min="1" max="1" width="20.4380952380952" style="1" customWidth="1"/>
     <col min="2" max="2" width="21.1047619047619" style="1" customWidth="1"/>
     <col min="3" max="3" width="29.3333333333333" style="1" customWidth="1"/>
     <col min="4" max="4" width="18.6666666666667" style="1" customWidth="1"/>
     <col min="5" max="5" width="16.3333333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14.4952380952381" customWidth="1"/>
+    <col min="7" max="7" width="13.847619047619" customWidth="1"/>
     <col min="10" max="10" width="21.552380952381" style="1" customWidth="1"/>
     <col min="11" max="11" width="24.3333333333333" style="1" customWidth="1"/>
+    <col min="12" max="12" width="18.4190476190476" customWidth="1"/>
+    <col min="13" max="13" width="16.8952380952381" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4202,75 +4276,113 @@
         <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:16">
       <c r="A2" s="1" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:16">
       <c r="A3" s="1" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:16">
       <c r="A4" s="1" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="F5" t="s">
         <v>121</v>
       </c>
-      <c r="J4" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="K4" s="1" t="s">
+      <c r="G5" t="s">
+        <v>131</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="M5" t="s">
         <v>46</v>
       </c>
     </row>
@@ -4345,19 +4457,19 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>21</v>

--- a/OurLib.xlsx
+++ b/OurLib.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\my-altium-library\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F17B557C-AB23-4EA5-8C72-C9D01AC9B2E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12885" tabRatio="500" firstSheet="2" activeTab="7"/>
+    <workbookView xWindow="14400" yWindow="0" windowWidth="14400" windowHeight="15600" tabRatio="500" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01 - Резисторы" sheetId="1" r:id="rId1"/>
@@ -38,12 +44,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="246">
   <si>
     <t>Part Number</t>
   </si>
@@ -772,178 +781,30 @@
   </si>
   <si>
     <t>Acustic.PcbLib</t>
+  </si>
+  <si>
+    <t>STM32F407</t>
+  </si>
+  <si>
+    <t>LQFP144-20x20mm</t>
+  </si>
+  <si>
+    <t>LQFP.PcbLib</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="_-* #,##0.00\ &quot;₽&quot;_-;\-* #,##0.00\ &quot;₽&quot;_-;_-* &quot;-&quot;??\ &quot;₽&quot;_-;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-* #,##0\ &quot;₽&quot;_-;\-* #,##0\ &quot;₽&quot;_-;_-* &quot;-&quot;\ &quot;₽&quot;_-;_-@_-"/>
-  </numFmts>
-  <fonts count="21">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="1"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="34">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -956,194 +817,8 @@
         <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1151,340 +826,167 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Запятая" xfId="1" builtinId="3"/>
-    <cellStyle name="Денежный" xfId="2" builtinId="4"/>
-    <cellStyle name="Процент" xfId="3" builtinId="5"/>
-    <cellStyle name="Запятая [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Денежный [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Гиперссылка" xfId="6" builtinId="8"/>
-    <cellStyle name="Открывавшаяся гиперссылка" xfId="7" builtinId="9"/>
-    <cellStyle name="Примечание" xfId="8" builtinId="10"/>
-    <cellStyle name="Предупреждающий текст" xfId="9" builtinId="11"/>
-    <cellStyle name="Заголовок" xfId="10" builtinId="15"/>
-    <cellStyle name="Пояснительный текст" xfId="11" builtinId="53"/>
-    <cellStyle name="Заголовок 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Заголовок 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Заголовок 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Заголовок 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Ввод" xfId="16" builtinId="20"/>
-    <cellStyle name="Вывод" xfId="17" builtinId="21"/>
-    <cellStyle name="Вычисление" xfId="18" builtinId="22"/>
-    <cellStyle name="Проверить ячейку" xfId="19" builtinId="23"/>
-    <cellStyle name="Связанная ячейка" xfId="20" builtinId="24"/>
-    <cellStyle name="Итого" xfId="21" builtinId="25"/>
-    <cellStyle name="Хороший" xfId="22" builtinId="26"/>
-    <cellStyle name="Плохой" xfId="23" builtinId="27"/>
-    <cellStyle name="Нейтральный" xfId="24" builtinId="28"/>
-    <cellStyle name="Акцент1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% — Акцент1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% — Акцент1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% — Акцент1" xfId="28" builtinId="32"/>
-    <cellStyle name="Акцент2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% — Акцент2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% — Акцент2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% — Акцент2" xfId="32" builtinId="36"/>
-    <cellStyle name="Акцент3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% — Акцент3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% — Акцент3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% — Акцент3" xfId="36" builtinId="40"/>
-    <cellStyle name="Акцент4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% — Акцент4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% — Акцент4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% — Акцент4" xfId="40" builtinId="44"/>
-    <cellStyle name="Акцент5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% — Акцент5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% — Акцент5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% — Акцент5" xfId="44" builtinId="48"/>
-    <cellStyle name="Акцент6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% — Акцент6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% — Акцент6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% — Акцент6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
       <border>
@@ -1495,7 +997,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="0"/>
       </font>
       <fill>
@@ -1523,154 +1025,40 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.39994506668294322"/>
         </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="16"/>
+      <tableStyleElement type="headerRow" dxfId="15"/>
+      <tableStyleElement type="totalRow" dxfId="14"/>
+      <tableStyleElement type="firstColumn" dxfId="13"/>
+      <tableStyleElement type="lastColumn" dxfId="12"/>
+      <tableStyleElement type="firstRowStripe" dxfId="11"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="9"/>
+      <tableStyleElement type="totalRow" dxfId="8"/>
+      <tableStyleElement type="firstRowStripe" dxfId="7"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
+      <tableStyleElement type="pageFieldValues" dxfId="0"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1729,7 +1117,7 @@
         <a:cs typeface=""/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1846,30 +1234,30 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N3"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="15" outlineLevelRow="2"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23" style="1" customWidth="1"/>
     <col min="2" max="2" width="19" style="1" customWidth="1"/>
-    <col min="3" max="3" width="30.1047619047619" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.3333333333333" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.4380952380952" style="1" customWidth="1"/>
-    <col min="6" max="6" width="14.6666666666667" style="1" customWidth="1"/>
-    <col min="7" max="7" width="14.552380952381" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.6666666666667" style="1" customWidth="1"/>
-    <col min="9" max="9" width="14.4380952380952" style="1" customWidth="1"/>
-    <col min="10" max="10" width="15.6666666666667" style="1" customWidth="1"/>
-    <col min="11" max="11" width="29.8857142857143" style="1" customWidth="1"/>
-    <col min="12" max="12" width="8.43809523809524" style="1" customWidth="1"/>
+    <col min="3" max="3" width="30.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.28515625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="29.85546875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="8.42578125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1913,7 +1301,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -1939,7 +1327,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>22</v>
       </c>
@@ -1956,29 +1344,27 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:N5"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="15" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.552380952381" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.3333333333333" style="1" customWidth="1"/>
-    <col min="4" max="4" width="16.552380952381" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.8857142857143" style="1" customWidth="1"/>
-    <col min="6" max="9" width="13.3333333333333" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.28515625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16.5703125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.85546875" style="1" customWidth="1"/>
+    <col min="6" max="9" width="13.28515625" style="1" customWidth="1"/>
     <col min="10" max="10" width="18" style="1" customWidth="1"/>
     <col min="11" max="11" width="30" style="1" customWidth="1"/>
-    <col min="12" max="12" width="5.55238095238095" style="1" customWidth="1"/>
-    <col min="13" max="14" width="5.33333333333333" style="1" customWidth="1"/>
+    <col min="12" max="12" width="5.5703125" style="1" customWidth="1"/>
+    <col min="13" max="14" width="5.28515625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2022,7 +1408,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>137</v>
       </c>
@@ -2048,7 +1434,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>144</v>
       </c>
@@ -2074,7 +1460,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>146</v>
       </c>
@@ -2100,7 +1486,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>148</v>
       </c>
@@ -2123,29 +1509,27 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:N6"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="15" outlineLevelRow="5"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.8857142857143" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.3333333333333" style="1" customWidth="1"/>
-    <col min="3" max="3" width="28.6666666666667" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.3333333333333" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.6666666666667" style="1" customWidth="1"/>
-    <col min="6" max="9" width="13.3333333333333" style="1" customWidth="1"/>
-    <col min="10" max="10" width="22.1047619047619" style="1" customWidth="1"/>
-    <col min="11" max="11" width="29.552380952381" style="1" customWidth="1"/>
-    <col min="12" max="12" width="5.55238095238095" style="1" customWidth="1"/>
-    <col min="13" max="14" width="5.33333333333333" style="1" customWidth="1"/>
+    <col min="1" max="1" width="28.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.28515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="28.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.28515625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" style="1" customWidth="1"/>
+    <col min="6" max="9" width="13.28515625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="22.140625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="29.5703125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="5.5703125" style="1" customWidth="1"/>
+    <col min="13" max="14" width="5.28515625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2189,7 +1573,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>151</v>
       </c>
@@ -2209,7 +1593,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>155</v>
       </c>
@@ -2229,7 +1613,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>157</v>
       </c>
@@ -2249,7 +1633,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>159</v>
       </c>
@@ -2269,7 +1653,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>161</v>
       </c>
@@ -2295,32 +1679,30 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:N16"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.8857142857143" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18.552380952381" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.3333333333333" style="1" customWidth="1"/>
-    <col min="4" max="4" width="18.6666666666667" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.6666666666667" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15.6666666666667" style="1" customWidth="1"/>
-    <col min="7" max="7" width="16.1047619047619" style="1" customWidth="1"/>
-    <col min="8" max="8" width="16.8857142857143" style="1" customWidth="1"/>
-    <col min="9" max="9" width="17.6666666666667" style="1" customWidth="1"/>
-    <col min="10" max="10" width="15.6666666666667" style="1" customWidth="1"/>
-    <col min="11" max="11" width="18.6666666666667" style="1" customWidth="1"/>
-    <col min="12" max="12" width="5.55238095238095" style="1" customWidth="1"/>
-    <col min="13" max="14" width="5.33333333333333" style="1" customWidth="1"/>
+    <col min="1" max="1" width="28.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.5703125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.28515625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.140625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="16.85546875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="17.7109375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="18.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="5.5703125" style="1" customWidth="1"/>
+    <col min="13" max="14" width="5.28515625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2364,7 +1746,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>165</v>
       </c>
@@ -2384,7 +1766,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>169</v>
       </c>
@@ -2404,7 +1786,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>170</v>
       </c>
@@ -2424,7 +1806,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>172</v>
       </c>
@@ -2447,7 +1829,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>176</v>
       </c>
@@ -2470,7 +1852,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>179</v>
       </c>
@@ -2493,7 +1875,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>182</v>
       </c>
@@ -2516,7 +1898,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>185</v>
       </c>
@@ -2539,7 +1921,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>188</v>
       </c>
@@ -2562,7 +1944,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>191</v>
       </c>
@@ -2585,7 +1967,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>194</v>
       </c>
@@ -2608,7 +1990,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>197</v>
       </c>
@@ -2631,7 +2013,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>200</v>
       </c>
@@ -2654,7 +2036,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>203</v>
       </c>
@@ -2677,7 +2059,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>206</v>
       </c>
@@ -2703,30 +2085,28 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:N3"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="15" outlineLevelRow="2"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.6666666666667" style="1" customWidth="1"/>
-    <col min="2" max="2" width="17.4380952380952" style="1" customWidth="1"/>
-    <col min="3" max="3" width="11.8857142857143" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.4380952380952" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.8857142857143" style="1" customWidth="1"/>
-    <col min="6" max="6" width="14.4380952380952" style="1" customWidth="1"/>
-    <col min="7" max="7" width="14.1047619047619" style="1" customWidth="1"/>
-    <col min="8" max="8" width="14.552380952381" style="1" customWidth="1"/>
-    <col min="9" max="9" width="17.1047619047619" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="17.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="11.85546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14.140625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="17.140625" style="1" customWidth="1"/>
     <col min="10" max="10" width="19" style="1" customWidth="1"/>
-    <col min="11" max="11" width="14.3333333333333" style="1" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2770,7 +2150,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>209</v>
       </c>
@@ -2787,7 +2167,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>213</v>
       </c>
@@ -2810,30 +2190,28 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="15" outlineLevelRow="1"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.1047619047619" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.4380952380952" style="1" customWidth="1"/>
-    <col min="3" max="3" width="12.1047619047619" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.6666666666667" style="1" customWidth="1"/>
+    <col min="1" max="1" width="12.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" style="1" customWidth="1"/>
     <col min="5" max="5" width="13" style="1" customWidth="1"/>
     <col min="6" max="6" width="15" style="1" customWidth="1"/>
-    <col min="7" max="7" width="15.3333333333333" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.1047619047619" style="1" customWidth="1"/>
-    <col min="9" max="9" width="15.3333333333333" style="1" customWidth="1"/>
-    <col min="10" max="10" width="15.552380952381" style="1" customWidth="1"/>
-    <col min="11" max="11" width="18.1047619047619" style="1" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.28515625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="15.5703125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="18.140625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2877,7 +2255,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>215</v>
       </c>
@@ -2900,26 +2278,24 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="15" outlineLevelRow="1"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.3333333333333" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.6666666666667" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.1047619047619" style="1" customWidth="1"/>
-    <col min="4" max="4" width="18.4380952380952" style="1" customWidth="1"/>
-    <col min="5" max="5" width="27.8857142857143" style="1" customWidth="1"/>
-    <col min="10" max="10" width="19.6666666666667" style="1" customWidth="1"/>
-    <col min="11" max="11" width="18.1047619047619" style="1" customWidth="1"/>
+    <col min="1" max="1" width="18.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="27.85546875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="19.7109375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="18.140625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2963,7 +2339,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>220</v>
       </c>
@@ -2986,30 +2362,28 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:N5"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="15" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.1047619047619" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.4380952380952" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.1047619047619" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.1047619047619" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.4380952380952" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15.1047619047619" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.6666666666667" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.3333333333333" style="1" customWidth="1"/>
-    <col min="9" max="9" width="14.552380952381" style="1" customWidth="1"/>
-    <col min="10" max="10" width="13.4380952380952" style="1" customWidth="1"/>
-    <col min="11" max="11" width="28.552380952381" style="1" customWidth="1"/>
+    <col min="1" max="1" width="16.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.7109375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.28515625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="28.5703125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3053,7 +2427,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>226</v>
       </c>
@@ -3073,7 +2447,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>232</v>
       </c>
@@ -3093,7 +2467,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>235</v>
       </c>
@@ -3113,7 +2487,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>236</v>
       </c>
@@ -3136,25 +2510,23 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:N3"/>
-  <sheetFormatPr defaultColWidth="9.1047619047619" defaultRowHeight="15" outlineLevelRow="2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.6666666666667" customWidth="1"/>
-    <col min="2" max="2" width="19.4380952380952" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" customWidth="1"/>
+    <col min="2" max="2" width="19.42578125" customWidth="1"/>
     <col min="3" max="3" width="17" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="10" max="10" width="20.1047619047619" customWidth="1"/>
-    <col min="11" max="11" width="15.6666666666667" customWidth="1"/>
+    <col min="10" max="10" width="20.140625" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3198,7 +2570,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>238</v>
       </c>
@@ -3209,7 +2581,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>241</v>
       </c>
@@ -3234,31 +2606,29 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:N3"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="15" outlineLevelRow="2"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.8857142857143" style="1" customWidth="1"/>
+    <col min="1" max="1" width="19.85546875" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" customWidth="1"/>
-    <col min="3" max="3" width="30.1047619047619" style="1" customWidth="1"/>
-    <col min="4" max="4" width="14.6666666666667" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.4380952380952" style="1" customWidth="1"/>
-    <col min="6" max="6" width="14.6666666666667" style="1" customWidth="1"/>
-    <col min="7" max="7" width="14.552380952381" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.6666666666667" style="1" customWidth="1"/>
-    <col min="9" max="9" width="14.4380952380952" style="1" customWidth="1"/>
-    <col min="10" max="10" width="17.6666666666667" style="1" customWidth="1"/>
-    <col min="11" max="11" width="35.8857142857143" style="1" customWidth="1"/>
-    <col min="12" max="12" width="8.43809523809524" style="1" customWidth="1"/>
+    <col min="3" max="3" width="30.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="35.85546875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="8.42578125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3302,7 +2672,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>24</v>
       </c>
@@ -3328,7 +2698,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>31</v>
       </c>
@@ -3360,26 +2730,24 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultColWidth="9.1047619047619" defaultRowHeight="15" outlineLevelRow="1"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.3333333333333" customWidth="1"/>
-    <col min="2" max="2" width="24.4380952380952" customWidth="1"/>
-    <col min="3" max="3" width="18.8857142857143" customWidth="1"/>
-    <col min="4" max="4" width="17.6666666666667" customWidth="1"/>
-    <col min="5" max="5" width="12.552380952381" customWidth="1"/>
-    <col min="10" max="10" width="19.8857142857143" customWidth="1"/>
+    <col min="1" max="1" width="22.28515625" customWidth="1"/>
+    <col min="2" max="2" width="24.42578125" customWidth="1"/>
+    <col min="3" max="3" width="18.85546875" customWidth="1"/>
+    <col min="4" max="4" width="17.7109375" customWidth="1"/>
+    <col min="5" max="5" width="12.5703125" customWidth="1"/>
+    <col min="10" max="10" width="19.85546875" customWidth="1"/>
     <col min="11" max="11" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3423,7 +2791,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>37</v>
       </c>
@@ -3448,30 +2816,28 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:N6"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="15" outlineLevelRow="5"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.4380952380952" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.6666666666667" style="1" customWidth="1"/>
-    <col min="3" max="3" width="26.6666666666667" style="1" customWidth="1"/>
-    <col min="4" max="4" width="18.4380952380952" style="1" customWidth="1"/>
+    <col min="1" max="1" width="22.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="26.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18.42578125" style="1" customWidth="1"/>
     <col min="5" max="5" width="15" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.6666666666667" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.1047619047619" style="1" customWidth="1"/>
-    <col min="8" max="8" width="13.8857142857143" style="1" customWidth="1"/>
-    <col min="9" max="9" width="12.6666666666667" style="1" customWidth="1"/>
-    <col min="10" max="10" width="19.3333333333333" style="1" customWidth="1"/>
-    <col min="11" max="11" width="27.552380952381" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13.85546875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="12.7109375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="19.28515625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="27.5703125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3515,7 +2881,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>41</v>
       </c>
@@ -3538,7 +2904,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>47</v>
       </c>
@@ -3555,7 +2921,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>49</v>
       </c>
@@ -3578,7 +2944,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>52</v>
       </c>
@@ -3601,7 +2967,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>56</v>
       </c>
@@ -3627,26 +2993,24 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:N11"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.3333333333333" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.552380952381" style="1" customWidth="1"/>
-    <col min="3" max="3" width="41.6666666666667" style="1" customWidth="1"/>
-    <col min="4" max="4" width="18.4380952380952" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.1047619047619" style="1" customWidth="1"/>
-    <col min="10" max="10" width="19.3333333333333" style="1" customWidth="1"/>
-    <col min="11" max="11" width="30.3333333333333" style="1" customWidth="1"/>
+    <col min="1" max="1" width="17.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="41.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.140625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="19.28515625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="30.28515625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3690,7 +3054,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>60</v>
       </c>
@@ -3713,7 +3077,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>65</v>
       </c>
@@ -3736,7 +3100,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>69</v>
       </c>
@@ -3759,7 +3123,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>72</v>
       </c>
@@ -3782,7 +3146,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>75</v>
       </c>
@@ -3805,7 +3169,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>78</v>
       </c>
@@ -3828,7 +3192,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>79</v>
       </c>
@@ -3842,7 +3206,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>81</v>
       </c>
@@ -3862,7 +3226,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>83</v>
       </c>
@@ -3882,7 +3246,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>86</v>
       </c>
@@ -3905,30 +3269,28 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:N5"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="15" outlineLevelRow="4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:N6"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.4380952380952" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.4380952380952" style="1" customWidth="1"/>
-    <col min="3" max="3" width="26.6666666666667" style="1" customWidth="1"/>
-    <col min="4" max="4" width="18.4380952380952" style="1" customWidth="1"/>
+    <col min="1" max="1" width="22.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="26.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18.42578125" style="1" customWidth="1"/>
     <col min="5" max="5" width="15" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.6666666666667" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.1047619047619" style="1" customWidth="1"/>
-    <col min="8" max="8" width="13.8857142857143" style="1" customWidth="1"/>
-    <col min="9" max="9" width="12.6666666666667" style="1" customWidth="1"/>
-    <col min="10" max="10" width="19.3333333333333" style="1" customWidth="1"/>
-    <col min="11" max="11" width="24.3333333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13.85546875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="12.7109375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="19.28515625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="24.28515625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3972,7 +3334,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>88</v>
       </c>
@@ -3992,7 +3354,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>93</v>
       </c>
@@ -4012,7 +3374,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>95</v>
       </c>
@@ -4032,7 +3394,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>97</v>
       </c>
@@ -4050,36 +3412,54 @@
       </c>
       <c r="K5" s="1" t="s">
         <v>92</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>245</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:N5"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="15" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.552380952381" style="1" customWidth="1"/>
-    <col min="2" max="2" width="29.3333333333333" style="1" customWidth="1"/>
-    <col min="3" max="3" width="19.3333333333333" style="1" customWidth="1"/>
+    <col min="1" max="1" width="16.5703125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="29.28515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="1" customWidth="1"/>
     <col min="4" max="4" width="15" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.1047619047619" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15.552380952381" style="1" customWidth="1"/>
-    <col min="7" max="7" width="15.1047619047619" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="15.140625" style="1" customWidth="1"/>
     <col min="8" max="8" width="14" style="1" customWidth="1"/>
-    <col min="9" max="9" width="14.6666666666667" style="1" customWidth="1"/>
-    <col min="10" max="10" width="17.8857142857143" style="1" customWidth="1"/>
-    <col min="11" max="11" width="18.552380952381" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.1047619047619" style="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="17.85546875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="18.5703125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.140625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4123,7 +3503,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>99</v>
       </c>
@@ -4146,7 +3526,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>105</v>
       </c>
@@ -4169,7 +3549,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>110</v>
       </c>
@@ -4192,7 +3572,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>113</v>
       </c>
@@ -4218,30 +3598,28 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:P5"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="15" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.4380952380952" style="1" customWidth="1"/>
-    <col min="2" max="2" width="21.1047619047619" style="1" customWidth="1"/>
-    <col min="3" max="3" width="29.3333333333333" style="1" customWidth="1"/>
-    <col min="4" max="4" width="18.6666666666667" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.3333333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="14.4952380952381" customWidth="1"/>
-    <col min="7" max="7" width="13.847619047619" customWidth="1"/>
-    <col min="10" max="10" width="21.552380952381" style="1" customWidth="1"/>
-    <col min="11" max="11" width="24.3333333333333" style="1" customWidth="1"/>
-    <col min="12" max="12" width="18.4190476190476" customWidth="1"/>
-    <col min="13" max="13" width="16.8952380952381" customWidth="1"/>
+    <col min="1" max="1" width="20.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="29.28515625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" customWidth="1"/>
+    <col min="7" max="7" width="13.85546875" customWidth="1"/>
+    <col min="10" max="10" width="21.5703125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="24.28515625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="18.42578125" customWidth="1"/>
+    <col min="13" max="13" width="16.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4291,7 +3669,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>118</v>
       </c>
@@ -4314,7 +3692,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>123</v>
       </c>
@@ -4334,7 +3712,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>126</v>
       </c>
@@ -4354,7 +3732,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>129</v>
       </c>
@@ -4389,29 +3767,27 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="15" outlineLevelRow="1"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.6666666666667" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20.3333333333333" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.3333333333333" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9.66666666666667" style="1" customWidth="1"/>
-    <col min="5" max="5" width="12.3333333333333" style="1" customWidth="1"/>
-    <col min="6" max="9" width="13.3333333333333" style="1" customWidth="1"/>
-    <col min="10" max="10" width="10.6666666666667" style="1" customWidth="1"/>
-    <col min="11" max="11" width="30.1047619047619" style="1" customWidth="1"/>
-    <col min="12" max="12" width="5.55238095238095" style="1" customWidth="1"/>
-    <col min="13" max="14" width="5.33333333333333" style="1" customWidth="1"/>
+    <col min="1" max="1" width="24.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.28515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.28515625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="12.28515625" style="1" customWidth="1"/>
+    <col min="6" max="9" width="13.28515625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.7109375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="30.140625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="5.5703125" style="1" customWidth="1"/>
+    <col min="13" max="14" width="5.28515625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4455,7 +3831,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>132</v>
       </c>
@@ -4478,6 +3854,5 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/OurLib.xlsx
+++ b/OurLib.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\my-altium-library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F17B557C-AB23-4EA5-8C72-C9D01AC9B2E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B9CC371-FA56-4A75-8352-898E4875CCDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14400" yWindow="0" windowWidth="14400" windowHeight="15600" tabRatio="500" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7200" yWindow="4215" windowWidth="21600" windowHeight="11385" tabRatio="500" firstSheet="4" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01 - Резисторы" sheetId="1" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="247">
   <si>
     <t>Part Number</t>
   </si>
@@ -790,6 +790,9 @@
   </si>
   <si>
     <t>LQFP.PcbLib</t>
+  </si>
+  <si>
+    <t>74HC165</t>
   </si>
 </sst>
 </file>
@@ -3603,7 +3606,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.42578125" style="1" customWidth="1"/>
@@ -3761,6 +3764,38 @@
         <v>77</v>
       </c>
       <c r="M5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="F6" t="s">
+        <v>121</v>
+      </c>
+      <c r="G6" t="s">
+        <v>131</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="M6" t="s">
         <v>46</v>
       </c>
     </row>

--- a/OurLib.xlsx
+++ b/OurLib.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\my-altium-library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B9CC371-FA56-4A75-8352-898E4875CCDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AD1F177-F807-424F-B788-8E7623505AD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7200" yWindow="4215" windowWidth="21600" windowHeight="11385" tabRatio="500" firstSheet="4" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" tabRatio="500" firstSheet="8" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01 - Резисторы" sheetId="1" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="713" uniqueCount="252">
   <si>
     <t>Part Number</t>
   </si>
@@ -793,16 +793,36 @@
   </si>
   <si>
     <t>74HC165</t>
+  </si>
+  <si>
+    <t>IDC-10F</t>
+  </si>
+  <si>
+    <t>PLS-1.27-10</t>
+  </si>
+  <si>
+    <t>PLS-1.27-N10</t>
+  </si>
+  <si>
+    <t>PLS-1.27-F10</t>
+  </si>
+  <si>
+    <t>BH-10R</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <charset val="1"/>
     </font>
@@ -1687,7 +1707,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.85546875" style="1" customWidth="1"/>
@@ -2085,9 +2105,73 @@
         <v>168</v>
       </c>
     </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
